--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="441">
   <si>
     <t xml:space="preserve">Event Name</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t xml:space="preserve">October Outdoor Learning Morning for Childminders and Children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broadmoor Lane Orchard Park. Bath</t>
   </si>
   <si>
     <t xml:space="preserve">https://beyth.co.uk/course/october-outdoor-learning-morning-for-childminders-and-children/</t>
@@ -1407,7 +1410,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1422,20 +1425,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF33CCCC"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFA500"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFA500"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF33CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1473,7 +1470,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1530,10 +1527,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1547,27 +1540,11 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF00B0F0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFA500"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1599,6 +1576,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF467886"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1650,7 +1635,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF92D050"/>
       <rgbColor rgb="FFFFC000"/>
-      <rgbColor rgb="FFFFA500"/>
+      <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF467886"/>
       <rgbColor rgb="FF969696"/>
@@ -2102,7 +2087,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="8" t="n">
@@ -2227,7 +2212,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="8" t="n">
@@ -2311,7 +2296,7 @@
         <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10</v>
@@ -2335,7 +2320,7 @@
         <v>29</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>31</v>
@@ -2352,8 +2337,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>60</v>
+      <c r="A7" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>46307</v>
@@ -2363,10 +2348,10 @@
         <v>Monday</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>37</v>
@@ -2381,13 +2366,13 @@
         <v>26</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>41</v>
@@ -2396,13 +2381,13 @@
         <v>29</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S7" s="10" t="s">
         <v>32</v>
@@ -2417,7 +2402,7 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>46308</v>
@@ -2427,7 +2412,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>23</v>
@@ -2451,7 +2436,7 @@
         <v>28</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>23</v>
@@ -2460,10 +2445,10 @@
         <v>29</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S8" s="10" t="s">
         <v>32</v>
@@ -2478,7 +2463,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>46309</v>
@@ -2488,10 +2473,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>37</v>
@@ -2506,22 +2491,22 @@
         <v>26</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S9" s="10" t="s">
         <v>32</v>
@@ -2535,8 +2520,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>77</v>
+      <c r="A10" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>46315</v>
@@ -2546,7 +2531,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>23</v>
@@ -2564,10 +2549,10 @@
         <v>26</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>23</v>
@@ -2579,13 +2564,13 @@
         <v>29</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S10" s="10" t="s">
         <v>32</v>
@@ -2599,8 +2584,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>82</v>
+      <c r="A11" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>46315</v>
@@ -2610,13 +2595,13 @@
         <v>Tuesday</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>16</v>
@@ -2634,7 +2619,7 @@
         <v>28</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>29</v>
@@ -2643,13 +2628,13 @@
         <v>29</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S11" s="10" t="s">
         <v>32</v>
@@ -2663,8 +2648,8 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>89</v>
+      <c r="A12" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>46316</v>
@@ -2674,10 +2659,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>37</v>
@@ -2692,13 +2677,13 @@
         <v>26</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>41</v>
@@ -2707,13 +2692,13 @@
         <v>29</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S12" s="10" t="s">
         <v>32</v>
@@ -2727,8 +2712,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>96</v>
+      <c r="A13" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>46317</v>
@@ -2738,10 +2723,10 @@
         <v>Thursday</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>37</v>
@@ -2759,13 +2744,13 @@
         <v>38</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>41</v>
@@ -2774,13 +2759,13 @@
         <v>29</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S13" s="10" t="s">
         <v>32</v>
@@ -2794,8 +2779,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>103</v>
+      <c r="A14" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>46317</v>
@@ -2805,10 +2790,10 @@
         <v>Thursday</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>37</v>
@@ -2823,13 +2808,13 @@
         <v>26</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>41</v>
@@ -2838,13 +2823,13 @@
         <v>29</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S14" s="10" t="s">
         <v>32</v>
@@ -2858,8 +2843,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>109</v>
+      <c r="A15" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>46318</v>
@@ -2869,7 +2854,7 @@
         <v>Friday</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>46</v>
@@ -2887,13 +2872,13 @@
         <v>26</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>41</v>
@@ -2902,13 +2887,13 @@
         <v>29</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S15" s="10" t="s">
         <v>32</v>
@@ -2923,7 +2908,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>46330</v>
@@ -2933,10 +2918,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>37</v>
@@ -2951,22 +2936,22 @@
         <v>26</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S16" s="10" t="s">
         <v>32</v>
@@ -2980,8 +2965,8 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>117</v>
+      <c r="A17" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>46331</v>
@@ -2991,7 +2976,7 @@
         <v>Thursday</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>36</v>
@@ -3009,7 +2994,7 @@
         <v>26</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>39</v>
@@ -3024,10 +3009,10 @@
         <v>29</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S17" s="10" t="s">
         <v>32</v>
@@ -3041,8 +3026,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>120</v>
+      <c r="A18" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>46332</v>
@@ -3052,13 +3037,13 @@
         <v>Friday</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>12</v>
@@ -3073,10 +3058,10 @@
         <v>27</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>41</v>
@@ -3085,13 +3070,13 @@
         <v>29</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S18" s="10" t="s">
         <v>32</v>
@@ -3105,8 +3090,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>126</v>
+      <c r="A19" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>46335</v>
@@ -3119,7 +3104,7 @@
         <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>37</v>
@@ -3137,13 +3122,13 @@
         <v>38</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>41</v>
@@ -3152,10 +3137,10 @@
         <v>29</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S19" s="10" t="s">
         <v>32</v>
@@ -3169,8 +3154,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>131</v>
+      <c r="A20" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>46336</v>
@@ -3180,13 +3165,13 @@
         <v>Tuesday</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>16</v>
@@ -3204,7 +3189,7 @@
         <v>28</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>41</v>
@@ -3213,13 +3198,13 @@
         <v>41</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S20" s="10" t="s">
         <v>32</v>
@@ -3233,8 +3218,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>132</v>
+      <c r="A21" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>46337</v>
@@ -3244,13 +3229,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>16</v>
@@ -3268,7 +3253,7 @@
         <v>28</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>41</v>
@@ -3277,13 +3262,13 @@
         <v>29</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="S21" s="10" t="s">
         <v>32</v>
@@ -3298,7 +3283,7 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>46338</v>
@@ -3308,10 +3293,10 @@
         <v>Thursday</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>70</v>
@@ -3329,20 +3314,20 @@
         <v>28</v>
       </c>
       <c r="L22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="S22" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="S22" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="T22" s="10" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3337,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>144</v>
+      <c r="A23" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>46344</v>
@@ -3363,10 +3348,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>37</v>
@@ -3381,19 +3366,19 @@
         <v>26</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>41</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S23" s="10" t="s">
         <v>32</v>
@@ -3407,8 +3392,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>145</v>
+      <c r="A24" s="7" t="s">
+        <v>146</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>46345</v>
@@ -3454,13 +3439,13 @@
         <v>29</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S24" s="10" t="s">
         <v>32</v>
@@ -3474,8 +3459,8 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>149</v>
+      <c r="A25" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>46351</v>
@@ -3485,10 +3470,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>37</v>
@@ -3503,13 +3488,13 @@
         <v>26</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>41</v>
@@ -3518,13 +3503,13 @@
         <v>29</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S25" s="10" t="s">
         <v>32</v>
@@ -3538,8 +3523,8 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>153</v>
+      <c r="A26" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>46352</v>
@@ -3549,7 +3534,7 @@
         <v>Thursday</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>36</v>
@@ -3567,10 +3552,10 @@
         <v>26</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>36</v>
@@ -3582,10 +3567,10 @@
         <v>29</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S26" s="10" t="s">
         <v>32</v>
@@ -3599,8 +3584,8 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>157</v>
+      <c r="A27" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>46352</v>
@@ -3649,10 +3634,10 @@
         <v>55</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S27" s="10" t="s">
         <v>32</v>
@@ -3794,7 +3779,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>46357</v>
@@ -3804,7 +3789,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>23</v>
@@ -3816,19 +3801,19 @@
         <v>100</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>23</v>
@@ -3837,10 +3822,10 @@
         <v>29</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S2" s="10" t="s">
         <v>32</v>
@@ -3854,8 +3839,8 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>168</v>
+      <c r="A3" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>46357</v>
@@ -3865,31 +3850,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>41</v>
@@ -3898,13 +3883,13 @@
         <v>41</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S3" s="10" t="s">
         <v>32</v>
@@ -3919,7 +3904,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>46358</v>
@@ -3941,19 +3926,19 @@
         <v>80</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>46</v>
@@ -3962,7 +3947,7 @@
         <v>29</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>49</v>
@@ -3979,8 +3964,8 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>173</v>
+      <c r="A5" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>46358</v>
@@ -3990,10 +3975,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>37</v>
@@ -4002,25 +3987,25 @@
         <v>80</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>41</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S5" s="10" t="s">
         <v>32</v>
@@ -4034,8 +4019,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>176</v>
+      <c r="A6" s="13" t="s">
+        <v>177</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>46358</v>
@@ -4045,31 +4030,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>41</v>
@@ -4078,10 +4063,10 @@
         <v>29</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S6" s="10" t="s">
         <v>32</v>
@@ -4095,8 +4080,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>181</v>
+      <c r="A7" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>46360</v>
@@ -4106,10 +4091,10 @@
         <v>Friday</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>37</v>
@@ -4118,22 +4103,22 @@
         <v>80</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>41</v>
@@ -4142,13 +4127,13 @@
         <v>29</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="S7" s="10" t="s">
         <v>32</v>
@@ -4162,8 +4147,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>186</v>
+      <c r="A8" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>46363</v>
@@ -4185,19 +4170,19 @@
         <v>80</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>36</v>
@@ -4209,10 +4194,10 @@
         <v>29</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="S8" s="10" t="s">
         <v>32</v>
@@ -4226,8 +4211,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>191</v>
+      <c r="A9" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>46364</v>
@@ -4237,10 +4222,10 @@
         <v>Tuesday</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>37</v>
@@ -4249,19 +4234,19 @@
         <v>80</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>41</v>
@@ -4270,13 +4255,13 @@
         <v>29</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S9" s="10" t="s">
         <v>32</v>
@@ -4290,8 +4275,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>197</v>
+      <c r="A10" s="13" t="s">
+        <v>198</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>46366</v>
@@ -4304,7 +4289,7 @@
         <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>37</v>
@@ -4313,22 +4298,22 @@
         <v>80</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>41</v>
@@ -4337,13 +4322,13 @@
         <v>29</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S10" s="10" t="s">
         <v>32</v>
@@ -4357,8 +4342,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>203</v>
+      <c r="A11" s="13" t="s">
+        <v>204</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>46394</v>
@@ -4368,7 +4353,7 @@
         <v>Thursday</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>46</v>
@@ -4380,19 +4365,19 @@
         <v>80</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>41</v>
@@ -4401,13 +4386,13 @@
         <v>29</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="S11" s="10" t="s">
         <v>32</v>
@@ -4421,8 +4406,8 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>206</v>
+      <c r="A12" s="13" t="s">
+        <v>207</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>46398</v>
@@ -4432,10 +4417,10 @@
         <v>Monday</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>37</v>
@@ -4444,19 +4429,19 @@
         <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>41</v>
@@ -4465,13 +4450,13 @@
         <v>29</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S12" s="10" t="s">
         <v>32</v>
@@ -4485,8 +4470,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>212</v>
+      <c r="A13" s="13" t="s">
+        <v>213</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>46400</v>
@@ -4496,10 +4481,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>37</v>
@@ -4508,19 +4493,19 @@
         <v>80</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>29</v>
@@ -4529,13 +4514,13 @@
         <v>29</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="S13" s="10" t="s">
         <v>32</v>
@@ -4549,8 +4534,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>217</v>
+      <c r="A14" s="13" t="s">
+        <v>218</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>46402</v>
@@ -4560,31 +4545,31 @@
         <v>Friday</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>20</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>41</v>
@@ -4593,13 +4578,13 @@
         <v>29</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S14" s="10" t="s">
         <v>32</v>
@@ -4613,8 +4598,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>222</v>
+      <c r="A15" s="13" t="s">
+        <v>223</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>46405</v>
@@ -4624,28 +4609,28 @@
         <v>Monday</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>52</v>
@@ -4657,10 +4642,10 @@
         <v>29</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S15" s="10" t="s">
         <v>32</v>
@@ -4674,8 +4659,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>228</v>
+      <c r="A16" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>46407</v>
@@ -4685,28 +4670,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>52</v>
@@ -4718,10 +4703,10 @@
         <v>29</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S16" s="10" t="s">
         <v>32</v>
@@ -4735,8 +4720,8 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>230</v>
+      <c r="A17" s="13" t="s">
+        <v>231</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>46407</v>
@@ -4746,7 +4731,7 @@
         <v>Wednesday</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -4758,19 +4743,19 @@
         <v>80</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>41</v>
@@ -4779,13 +4764,13 @@
         <v>29</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="S17" s="10" t="s">
         <v>32</v>
@@ -4799,8 +4784,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>234</v>
+      <c r="A18" s="13" t="s">
+        <v>235</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>46408</v>
@@ -4813,7 +4798,7 @@
         <v>35</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>37</v>
@@ -4822,22 +4807,22 @@
         <v>80</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>41</v>
@@ -4846,10 +4831,10 @@
         <v>29</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S18" s="10" t="s">
         <v>32</v>
@@ -4863,8 +4848,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>238</v>
+      <c r="A19" s="13" t="s">
+        <v>239</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>46408</v>
@@ -4874,10 +4859,10 @@
         <v>Thursday</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>37</v>
@@ -4886,19 +4871,19 @@
         <v>80</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>41</v>
@@ -4907,13 +4892,13 @@
         <v>29</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="S19" s="10" t="s">
         <v>32</v>
@@ -4927,8 +4912,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>244</v>
+      <c r="A20" s="13" t="s">
+        <v>245</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>46414</v>
@@ -4938,10 +4923,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>37</v>
@@ -4950,19 +4935,19 @@
         <v>80</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>29</v>
@@ -4971,13 +4956,13 @@
         <v>29</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="S20" s="10" t="s">
         <v>32</v>
@@ -4991,8 +4976,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>249</v>
+      <c r="A21" s="13" t="s">
+        <v>250</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>46416</v>
@@ -5002,7 +4987,7 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>36</v>
@@ -5014,16 +4999,16 @@
         <v>24</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>36</v>
@@ -5035,10 +5020,10 @@
         <v>29</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="S21" s="10" t="s">
         <v>32</v>
@@ -5052,8 +5037,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>253</v>
+      <c r="A22" s="13" t="s">
+        <v>254</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>46420</v>
@@ -5063,10 +5048,10 @@
         <v>Tuesday</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>37</v>
@@ -5075,22 +5060,22 @@
         <v>80</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>41</v>
@@ -5099,13 +5084,13 @@
         <v>29</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="S22" s="10" t="s">
         <v>32</v>
@@ -5119,8 +5104,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>257</v>
+      <c r="A23" s="13" t="s">
+        <v>258</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>46420</v>
@@ -5130,28 +5115,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>52</v>
@@ -5163,13 +5148,13 @@
         <v>29</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S23" s="10" t="s">
         <v>32</v>
@@ -5183,8 +5168,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>262</v>
+      <c r="A24" s="13" t="s">
+        <v>263</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>46420</v>
@@ -5194,7 +5179,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>23</v>
@@ -5206,16 +5191,16 @@
         <v>40</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>23</v>
@@ -5227,13 +5212,13 @@
         <v>29</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S24" s="10" t="s">
         <v>32</v>
@@ -5247,8 +5232,8 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>266</v>
+      <c r="A25" s="13" t="s">
+        <v>267</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>46421</v>
@@ -5258,31 +5243,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>41</v>
@@ -5291,10 +5276,10 @@
         <v>29</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S25" s="10" t="s">
         <v>32</v>
@@ -5308,8 +5293,8 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>268</v>
+      <c r="A26" s="13" t="s">
+        <v>269</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>46421</v>
@@ -5331,19 +5316,19 @@
         <v>80</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>46</v>
@@ -5352,7 +5337,7 @@
         <v>29</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>49</v>
@@ -5369,8 +5354,8 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>270</v>
+      <c r="A27" s="13" t="s">
+        <v>271</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>46422</v>
@@ -5380,28 +5365,28 @@
         <v>Thursday</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>52</v>
@@ -5413,13 +5398,13 @@
         <v>29</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S27" s="10" t="s">
         <v>32</v>
@@ -5433,8 +5418,8 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>272</v>
+      <c r="A28" s="13" t="s">
+        <v>273</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>46422</v>
@@ -5444,10 +5429,10 @@
         <v>Thursday</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>37</v>
@@ -5456,19 +5441,19 @@
         <v>80</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>41</v>
@@ -5477,13 +5462,13 @@
         <v>29</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="S28" s="10" t="s">
         <v>32</v>
@@ -5497,8 +5482,8 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>275</v>
+      <c r="A29" s="13" t="s">
+        <v>276</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>46423</v>
@@ -5508,7 +5493,7 @@
         <v>Friday</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>36</v>
@@ -5520,16 +5505,16 @@
         <v>24</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>36</v>
@@ -5541,10 +5526,10 @@
         <v>29</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="S29" s="10" t="s">
         <v>32</v>
@@ -5558,8 +5543,8 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
-        <v>277</v>
+      <c r="A30" s="13" t="s">
+        <v>278</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>46426</v>
@@ -5581,19 +5566,19 @@
         <v>80</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>36</v>
@@ -5605,10 +5590,10 @@
         <v>29</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="S30" s="10" t="s">
         <v>32</v>
@@ -5622,8 +5607,8 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>280</v>
+      <c r="A31" s="13" t="s">
+        <v>281</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>46427</v>
@@ -5633,7 +5618,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>46</v>
@@ -5645,19 +5630,19 @@
         <v>80</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>41</v>
@@ -5666,13 +5651,13 @@
         <v>29</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S31" s="10" t="s">
         <v>32</v>
@@ -5686,8 +5671,8 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
-        <v>283</v>
+      <c r="A32" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>46428</v>
@@ -5697,10 +5682,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>37</v>
@@ -5709,19 +5694,19 @@
         <v>80</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>29</v>
@@ -5730,10 +5715,10 @@
         <v>41</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S32" s="10" t="s">
         <v>32</v>
@@ -5747,8 +5732,8 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>284</v>
+      <c r="A33" s="12" t="s">
+        <v>285</v>
       </c>
       <c r="B33" s="8" t="n">
         <v>46428</v>
@@ -5758,10 +5743,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>37</v>
@@ -5770,19 +5755,19 @@
         <v>80</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>29</v>
@@ -5791,10 +5776,10 @@
         <v>41</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="S33" s="10" t="s">
         <v>32</v>
@@ -5808,8 +5793,8 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
-        <v>285</v>
+      <c r="A34" s="13" t="s">
+        <v>286</v>
       </c>
       <c r="B34" s="8" t="n">
         <v>46430</v>
@@ -5819,7 +5804,7 @@
         <v>Friday</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>36</v>
@@ -5831,16 +5816,16 @@
         <v>24</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>36</v>
@@ -5852,10 +5837,10 @@
         <v>29</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="S34" s="10" t="s">
         <v>32</v>
@@ -5869,8 +5854,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="s">
-        <v>287</v>
+      <c r="A35" s="13" t="s">
+        <v>288</v>
       </c>
       <c r="B35" s="8" t="n">
         <v>46441</v>
@@ -5883,7 +5868,7 @@
         <v>35</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>37</v>
@@ -5892,22 +5877,22 @@
         <v>80</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>41</v>
@@ -5916,13 +5901,13 @@
         <v>29</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S35" s="10" t="s">
         <v>32</v>
@@ -5936,8 +5921,8 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="s">
-        <v>289</v>
+      <c r="A36" s="13" t="s">
+        <v>290</v>
       </c>
       <c r="B36" s="8" t="n">
         <v>46444</v>
@@ -5947,7 +5932,7 @@
         <v>Friday</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>23</v>
@@ -5959,19 +5944,19 @@
         <v>100</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>23</v>
@@ -5983,10 +5968,10 @@
         <v>29</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S36" s="10" t="s">
         <v>32</v>
@@ -6125,8 +6110,8 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>293</v>
+      <c r="A2" s="13" t="s">
+        <v>294</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>46448</v>
@@ -6136,28 +6121,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>52</v>
@@ -6168,11 +6153,11 @@
       <c r="O2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="15" t="s">
-        <v>299</v>
+      <c r="Q2" s="14" t="s">
+        <v>300</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S2" s="10" t="s">
         <v>32</v>
@@ -6186,8 +6171,8 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>301</v>
+      <c r="A3" s="13" t="s">
+        <v>302</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>46449</v>
@@ -6197,10 +6182,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>37</v>
@@ -6209,19 +6194,19 @@
         <v>80</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>41</v>
@@ -6230,13 +6215,13 @@
         <v>29</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>304</v>
+        <v>242</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>305</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S3" s="10" t="s">
         <v>32</v>
@@ -6250,8 +6235,8 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>306</v>
+      <c r="A4" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>46450</v>
@@ -6273,19 +6258,19 @@
         <v>80</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>36</v>
@@ -6297,13 +6282,13 @@
         <v>29</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q4" s="15" t="s">
-        <v>310</v>
+        <v>147</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>311</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S4" s="10" t="s">
         <v>32</v>
@@ -6317,8 +6302,8 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>311</v>
+      <c r="A5" s="13" t="s">
+        <v>312</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>46455</v>
@@ -6328,10 +6313,10 @@
         <v>Tuesday</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>37</v>
@@ -6340,19 +6325,19 @@
         <v>80</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>41</v>
@@ -6361,13 +6346,13 @@
         <v>29</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="S5" s="10" t="s">
         <v>32</v>
@@ -6381,8 +6366,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>315</v>
+      <c r="A6" s="12" t="s">
+        <v>316</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>46456</v>
@@ -6392,10 +6377,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>37</v>
@@ -6404,19 +6389,19 @@
         <v>80</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>29</v>
@@ -6425,11 +6410,11 @@
         <v>41</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q6" s="15" t="s">
         <v>215</v>
       </c>
+      <c r="Q6" s="14" t="s">
+        <v>216</v>
+      </c>
       <c r="S6" s="10" t="s">
         <v>32</v>
       </c>
@@ -6442,8 +6427,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>316</v>
+      <c r="A7" s="13" t="s">
+        <v>317</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>46456</v>
@@ -6453,7 +6438,7 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>46</v>
@@ -6465,19 +6450,19 @@
         <v>80</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>41</v>
@@ -6486,13 +6471,13 @@
         <v>29</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q7" s="15" t="s">
-        <v>318</v>
+        <v>232</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>319</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="S7" s="10" t="s">
         <v>32</v>
@@ -6506,8 +6491,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>153</v>
+      <c r="A8" s="13" t="s">
+        <v>154</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>46457</v>
@@ -6517,7 +6502,7 @@
         <v>Thursday</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>36</v>
@@ -6529,16 +6514,16 @@
         <v>80</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>36</v>
@@ -6549,11 +6534,11 @@
       <c r="O8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q8" s="15" t="s">
-        <v>321</v>
+      <c r="Q8" s="14" t="s">
+        <v>322</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S8" s="10" t="s">
         <v>32</v>
@@ -6567,8 +6552,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>322</v>
+      <c r="A9" s="13" t="s">
+        <v>323</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>46462</v>
@@ -6581,7 +6566,7 @@
         <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>37</v>
@@ -6590,22 +6575,22 @@
         <v>80</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>41</v>
@@ -6613,11 +6598,11 @@
       <c r="O9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" s="15" t="s">
-        <v>324</v>
+      <c r="Q9" s="14" t="s">
+        <v>325</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S9" s="10" t="s">
         <v>32</v>
@@ -6631,8 +6616,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>325</v>
+      <c r="A10" s="13" t="s">
+        <v>326</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>46462</v>
@@ -6642,7 +6627,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>46</v>
@@ -6654,19 +6639,19 @@
         <v>80</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>41</v>
@@ -6675,13 +6660,13 @@
         <v>29</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>327</v>
+        <v>247</v>
+      </c>
+      <c r="Q10" s="14" t="s">
+        <v>328</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S10" s="10" t="s">
         <v>32</v>
@@ -6695,8 +6680,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>329</v>
+      <c r="A11" s="13" t="s">
+        <v>330</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>46463</v>
@@ -6718,19 +6703,19 @@
         <v>80</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>52</v>
@@ -6744,11 +6729,11 @@
       <c r="P11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q11" s="15" t="s">
-        <v>331</v>
+      <c r="Q11" s="14" t="s">
+        <v>332</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="S11" s="10" t="s">
         <v>32</v>
@@ -6762,8 +6747,8 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>333</v>
+      <c r="A12" s="13" t="s">
+        <v>334</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>46464</v>
@@ -6773,10 +6758,10 @@
         <v>Thursday</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>37</v>
@@ -6785,22 +6770,22 @@
         <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>41</v>
@@ -6808,11 +6793,11 @@
       <c r="O12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q12" s="15" t="s">
-        <v>336</v>
+      <c r="Q12" s="14" t="s">
+        <v>337</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S12" s="10" t="s">
         <v>32</v>
@@ -6826,8 +6811,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>338</v>
+      <c r="A13" s="13" t="s">
+        <v>339</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>46468</v>
@@ -6849,19 +6834,19 @@
         <v>80</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>36</v>
@@ -6872,11 +6857,11 @@
       <c r="O13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q13" s="15" t="s">
-        <v>339</v>
+      <c r="Q13" s="14" t="s">
+        <v>340</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="S13" s="10" t="s">
         <v>32</v>
@@ -6890,8 +6875,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>341</v>
+      <c r="A14" s="13" t="s">
+        <v>342</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>46469</v>
@@ -6901,31 +6886,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>20</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>41</v>
@@ -6934,13 +6919,13 @@
         <v>29</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q14" s="15" t="s">
         <v>346</v>
       </c>
+      <c r="Q14" s="14" t="s">
+        <v>347</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S14" s="10" t="s">
         <v>32</v>
@@ -6954,8 +6939,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>348</v>
+      <c r="A15" s="13" t="s">
+        <v>349</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>46470</v>
@@ -6977,19 +6962,19 @@
         <v>80</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>46</v>
@@ -6997,8 +6982,8 @@
       <c r="O15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" s="15" t="s">
-        <v>350</v>
+      <c r="Q15" s="14" t="s">
+        <v>351</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>49</v>
@@ -7015,8 +7000,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>351</v>
+      <c r="A16" s="13" t="s">
+        <v>352</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>46486</v>
@@ -7026,10 +7011,10 @@
         <v>Friday</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>37</v>
@@ -7038,22 +7023,22 @@
         <v>80</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>41</v>
@@ -7062,13 +7047,13 @@
         <v>29</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>353</v>
+        <v>101</v>
+      </c>
+      <c r="Q16" s="14" t="s">
+        <v>354</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S16" s="10" t="s">
         <v>32</v>
@@ -7082,8 +7067,8 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>355</v>
+      <c r="A17" s="13" t="s">
+        <v>356</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>46492</v>
@@ -7093,7 +7078,7 @@
         <v>Thursday</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>36</v>
@@ -7105,16 +7090,16 @@
         <v>80</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>36</v>
@@ -7126,13 +7111,13 @@
         <v>29</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q17" s="15" t="s">
         <v>357</v>
       </c>
+      <c r="Q17" s="14" t="s">
+        <v>358</v>
+      </c>
       <c r="R17" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S17" s="10" t="s">
         <v>32</v>
@@ -7146,8 +7131,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>359</v>
+      <c r="A18" s="13" t="s">
+        <v>360</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>46496</v>
@@ -7157,7 +7142,7 @@
         <v>Monday</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>23</v>
@@ -7169,19 +7154,19 @@
         <v>100</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>23</v>
@@ -7192,11 +7177,11 @@
       <c r="O18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q18" s="15" t="s">
-        <v>361</v>
+      <c r="Q18" s="14" t="s">
+        <v>362</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S18" s="10" t="s">
         <v>32</v>
@@ -7210,8 +7195,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>362</v>
+      <c r="A19" s="13" t="s">
+        <v>363</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>46500</v>
@@ -7221,31 +7206,31 @@
         <v>Friday</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>16</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>41</v>
@@ -7254,13 +7239,13 @@
         <v>29</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S19" s="10" t="s">
         <v>32</v>
@@ -7274,8 +7259,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>367</v>
+      <c r="A20" s="13" t="s">
+        <v>368</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>46505</v>
@@ -7285,28 +7270,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>6</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>52</v>
@@ -7317,11 +7302,11 @@
       <c r="O20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q20" s="15" t="s">
-        <v>368</v>
+      <c r="Q20" s="14" t="s">
+        <v>369</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S20" s="10" t="s">
         <v>32</v>
@@ -7335,8 +7320,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>369</v>
+      <c r="A21" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>46506</v>
@@ -7346,7 +7331,7 @@
         <v>Thursday</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>36</v>
@@ -7358,16 +7343,16 @@
         <v>80</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>36</v>
@@ -7379,13 +7364,13 @@
         <v>41</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S21" s="10" t="s">
         <v>32</v>
@@ -7399,8 +7384,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>109</v>
+      <c r="A22" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>46507</v>
@@ -7410,7 +7395,7 @@
         <v>Friday</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>46</v>
@@ -7422,19 +7407,19 @@
         <v>80</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>41</v>
@@ -7443,13 +7428,13 @@
         <v>29</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q22" s="15" t="s">
-        <v>370</v>
+        <v>112</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>371</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S22" s="10" t="s">
         <v>32</v>
@@ -7463,8 +7448,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>371</v>
+      <c r="A23" s="13" t="s">
+        <v>372</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>46512</v>
@@ -7474,10 +7459,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>37</v>
@@ -7486,22 +7471,22 @@
         <v>80</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>41</v>
@@ -7509,11 +7494,11 @@
       <c r="O23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q23" s="15" t="s">
-        <v>373</v>
+      <c r="Q23" s="14" t="s">
+        <v>374</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S23" s="10" t="s">
         <v>32</v>
@@ -7527,8 +7512,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>374</v>
+      <c r="A24" s="13" t="s">
+        <v>375</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>46512</v>
@@ -7550,19 +7535,19 @@
         <v>80</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>46</v>
@@ -7570,8 +7555,8 @@
       <c r="O24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q24" s="15" t="s">
-        <v>375</v>
+      <c r="Q24" s="14" t="s">
+        <v>376</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>49</v>
@@ -7588,8 +7573,8 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>117</v>
+      <c r="A25" s="13" t="s">
+        <v>118</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>46513</v>
@@ -7599,7 +7584,7 @@
         <v>Thursday</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>36</v>
@@ -7611,16 +7596,16 @@
         <v>80</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>36</v>
@@ -7631,11 +7616,11 @@
       <c r="O25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q25" s="15" t="s">
-        <v>376</v>
+      <c r="Q25" s="14" t="s">
+        <v>377</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S25" s="10" t="s">
         <v>32</v>
@@ -7649,8 +7634,8 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>377</v>
+      <c r="A26" s="13" t="s">
+        <v>378</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>46518</v>
@@ -7663,7 +7648,7 @@
         <v>35</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>37</v>
@@ -7672,22 +7657,22 @@
         <v>80</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>41</v>
@@ -7696,13 +7681,13 @@
         <v>29</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q26" s="15" t="s">
-        <v>379</v>
+        <v>201</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>380</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S26" s="10" t="s">
         <v>32</v>
@@ -7716,8 +7701,8 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>380</v>
+      <c r="A27" s="13" t="s">
+        <v>381</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>46519</v>
@@ -7727,10 +7712,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>37</v>
@@ -7739,19 +7724,19 @@
         <v>80</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>29</v>
@@ -7760,13 +7745,13 @@
         <v>29</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q27" s="15" t="s">
-        <v>381</v>
+        <v>215</v>
+      </c>
+      <c r="Q27" s="14" t="s">
+        <v>382</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="S27" s="10" t="s">
         <v>32</v>
@@ -7780,8 +7765,8 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>382</v>
+      <c r="A28" s="13" t="s">
+        <v>383</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>46520</v>
@@ -7791,10 +7776,10 @@
         <v>Thursday</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>37</v>
@@ -7803,19 +7788,19 @@
         <v>80</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>29</v>
@@ -7823,11 +7808,11 @@
       <c r="O28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q28" s="15" t="s">
-        <v>384</v>
+      <c r="Q28" s="14" t="s">
+        <v>385</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S28" s="10" t="s">
         <v>32</v>
@@ -7841,8 +7826,8 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>386</v>
+      <c r="A29" s="13" t="s">
+        <v>387</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>46525</v>
@@ -7864,19 +7849,19 @@
         <v>80</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>52</v>
@@ -7890,11 +7875,11 @@
       <c r="P29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q29" s="15" t="s">
-        <v>387</v>
+      <c r="Q29" s="14" t="s">
+        <v>388</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S29" s="10" t="s">
         <v>32</v>
@@ -7908,8 +7893,8 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
-        <v>132</v>
+      <c r="A30" s="13" t="s">
+        <v>133</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>46526</v>
@@ -7919,31 +7904,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>16</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>41</v>
@@ -7952,13 +7937,13 @@
         <v>29</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q30" s="15" t="s">
-        <v>389</v>
+        <v>136</v>
+      </c>
+      <c r="Q30" s="14" t="s">
+        <v>390</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="S30" s="10" t="s">
         <v>32</v>
@@ -7972,8 +7957,8 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>390</v>
+      <c r="A31" s="12" t="s">
+        <v>391</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>46527</v>
@@ -7983,7 +7968,7 @@
         <v>Thursday</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>36</v>
@@ -7995,16 +7980,16 @@
         <v>80</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>36</v>
@@ -8016,13 +8001,13 @@
         <v>41</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S31" s="10" t="s">
         <v>32</v>
@@ -8036,8 +8021,8 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
-        <v>391</v>
+      <c r="A32" s="13" t="s">
+        <v>392</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>46533</v>
@@ -8047,31 +8032,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>41</v>
@@ -8079,11 +8064,11 @@
       <c r="O32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q32" s="15" t="s">
-        <v>392</v>
+      <c r="Q32" s="14" t="s">
+        <v>393</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S32" s="10" t="s">
         <v>32</v>
@@ -8097,8 +8082,8 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>393</v>
+      <c r="A33" s="12" t="s">
+        <v>394</v>
       </c>
       <c r="B33" s="8" t="n">
         <v>46534</v>
@@ -8108,10 +8093,10 @@
         <v>Thursday</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>37</v>
@@ -8120,19 +8105,19 @@
         <v>80</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>29</v>
@@ -8141,7 +8126,7 @@
         <v>41</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="S33" s="10" t="s">
         <v>32</v>
@@ -8274,8 +8259,8 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>394</v>
+      <c r="A2" s="13" t="s">
+        <v>395</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>46547</v>
@@ -8285,10 +8270,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -8297,22 +8282,22 @@
         <v>80</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>41</v>
@@ -8321,13 +8306,13 @@
         <v>29</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>400</v>
+        <v>101</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>401</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="S2" s="10" t="s">
         <v>32</v>
@@ -8341,8 +8326,8 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>402</v>
+      <c r="A3" s="13" t="s">
+        <v>403</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>46548</v>
@@ -8364,19 +8349,19 @@
         <v>80</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>36</v>
@@ -8388,13 +8373,13 @@
         <v>29</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>405</v>
+        <v>147</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S3" s="10" t="s">
         <v>32</v>
@@ -8408,8 +8393,8 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>406</v>
+      <c r="A4" s="13" t="s">
+        <v>407</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>46552</v>
@@ -8419,7 +8404,7 @@
         <v>Monday</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>46</v>
@@ -8431,19 +8416,19 @@
         <v>80</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>41</v>
@@ -8452,13 +8437,13 @@
         <v>29</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q4" s="15" t="s">
-        <v>408</v>
+        <v>210</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>409</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="S4" s="10" t="s">
         <v>32</v>
@@ -8472,8 +8457,8 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>410</v>
+      <c r="A5" s="13" t="s">
+        <v>411</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>46553</v>
@@ -8483,7 +8468,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>23</v>
@@ -8495,19 +8480,19 @@
         <v>100</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>23</v>
@@ -8518,11 +8503,11 @@
       <c r="O5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" s="15" t="s">
-        <v>413</v>
+      <c r="Q5" s="14" t="s">
+        <v>414</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S5" s="10" t="s">
         <v>32</v>
@@ -8536,8 +8521,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>414</v>
+      <c r="A6" s="12" t="s">
+        <v>415</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>46554</v>
@@ -8547,10 +8532,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>37</v>
@@ -8559,19 +8544,19 @@
         <v>80</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>29</v>
@@ -8580,10 +8565,10 @@
         <v>41</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q6" s="15" t="s">
-        <v>381</v>
+        <v>215</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>382</v>
       </c>
       <c r="S6" s="10" t="s">
         <v>32</v>
@@ -8597,8 +8582,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>415</v>
+      <c r="A7" s="13" t="s">
+        <v>416</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>46561</v>
@@ -8608,10 +8593,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>37</v>
@@ -8620,19 +8605,19 @@
         <v>80</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>29</v>
@@ -8641,13 +8626,13 @@
         <v>29</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q7" s="15" t="s">
-        <v>416</v>
+        <v>247</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>417</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="S7" s="10" t="s">
         <v>32</v>
@@ -8661,8 +8646,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>418</v>
+      <c r="A8" s="13" t="s">
+        <v>419</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>46562</v>
@@ -8675,7 +8660,7 @@
         <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>37</v>
@@ -8684,22 +8669,22 @@
         <v>80</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>41</v>
@@ -8708,10 +8693,10 @@
         <v>29</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S8" s="10" t="s">
         <v>32</v>
@@ -8725,8 +8710,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>421</v>
+      <c r="A9" s="13" t="s">
+        <v>422</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>46568</v>
@@ -8748,19 +8733,19 @@
         <v>80</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>46</v>
@@ -8768,8 +8753,8 @@
       <c r="O9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" s="15" t="s">
-        <v>423</v>
+      <c r="Q9" s="14" t="s">
+        <v>424</v>
       </c>
       <c r="R9" s="1" t="s">
         <v>49</v>
@@ -8786,8 +8771,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>424</v>
+      <c r="A10" s="13" t="s">
+        <v>425</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>46569</v>
@@ -8797,10 +8782,10 @@
         <v>Thursday</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>37</v>
@@ -8809,22 +8794,22 @@
         <v>80</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>41</v>
@@ -8832,11 +8817,11 @@
       <c r="O10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="15" t="s">
-        <v>426</v>
+      <c r="Q10" s="14" t="s">
+        <v>427</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S10" s="10" t="s">
         <v>32</v>
@@ -8850,8 +8835,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>427</v>
+      <c r="A11" s="13" t="s">
+        <v>428</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>46570</v>
@@ -8861,31 +8846,31 @@
         <v>Friday</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>16</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>41</v>
@@ -8894,13 +8879,13 @@
         <v>29</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>429</v>
+        <v>112</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>430</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="S11" s="10" t="s">
         <v>32</v>
@@ -8914,8 +8899,8 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>431</v>
+      <c r="A12" s="12" t="s">
+        <v>432</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>46575</v>
@@ -8925,10 +8910,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>37</v>
@@ -8937,19 +8922,19 @@
         <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>29</v>
@@ -8958,10 +8943,10 @@
         <v>41</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>416</v>
+        <v>247</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>417</v>
       </c>
       <c r="S12" s="10" t="s">
         <v>32</v>
@@ -8975,8 +8960,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>432</v>
+      <c r="A13" s="12" t="s">
+        <v>433</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>46575</v>
@@ -8986,10 +8971,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>37</v>
@@ -8998,19 +8983,19 @@
         <v>80</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>29</v>
@@ -9019,10 +9004,10 @@
         <v>41</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q13" s="15" t="s">
-        <v>381</v>
+        <v>215</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>382</v>
       </c>
       <c r="S13" s="10" t="s">
         <v>32</v>
@@ -9036,8 +9021,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>203</v>
+      <c r="A14" s="13" t="s">
+        <v>204</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>46576</v>
@@ -9047,7 +9032,7 @@
         <v>Thursday</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>46</v>
@@ -9059,19 +9044,19 @@
         <v>80</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>41</v>
@@ -9080,13 +9065,13 @@
         <v>29</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q14" s="15" t="s">
-        <v>433</v>
+        <v>112</v>
+      </c>
+      <c r="Q14" s="14" t="s">
+        <v>434</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="S14" s="10" t="s">
         <v>32</v>
@@ -9100,8 +9085,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>434</v>
+      <c r="A15" s="12" t="s">
+        <v>435</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>46589</v>
@@ -9111,10 +9096,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>37</v>
@@ -9123,19 +9108,19 @@
         <v>80</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>29</v>
@@ -9144,10 +9129,10 @@
         <v>41</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q15" s="15" t="s">
-        <v>416</v>
+        <v>247</v>
+      </c>
+      <c r="Q15" s="14" t="s">
+        <v>417</v>
       </c>
       <c r="S15" s="10" t="s">
         <v>32</v>
@@ -9161,8 +9146,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>435</v>
+      <c r="A16" s="13" t="s">
+        <v>436</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>46612</v>
@@ -9172,10 +9157,10 @@
         <v>Friday</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>37</v>
@@ -9184,22 +9169,22 @@
         <v>80</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>41</v>
@@ -9208,13 +9193,13 @@
         <v>29</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q16" s="15" t="s">
         <v>438</v>
       </c>
+      <c r="Q16" s="14" t="s">
+        <v>439</v>
+      </c>
       <c r="R16" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="S16" s="10" t="s">
         <v>32</v>

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67D35EE-E409-4B89-9FB5-72D978B617A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387ABC69-274C-4A9A-BC02-40E865A4E124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32805" yWindow="2370" windowWidth="34740" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -1406,7 +1406,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1443,6 +1443,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor rgb="FF33CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1456,7 +1462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1480,6 +1486,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4884,7 +4893,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="15" t="s">
         <v>250</v>
       </c>
       <c r="B21" s="7">
@@ -5390,7 +5399,7 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="15" t="s">
         <v>276</v>
       </c>
       <c r="B29" s="7">
@@ -5701,7 +5710,7 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="15" t="s">
         <v>286</v>
       </c>
       <c r="B34" s="7">

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387ABC69-274C-4A9A-BC02-40E865A4E124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A6D635-DB05-4247-BB21-65890416DC9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32805" yWindow="2370" windowWidth="34740" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -1406,7 +1406,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1449,6 +1449,12 @@
         <bgColor rgb="FF33CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1485,10 +1491,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4893,7 +4899,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>250</v>
       </c>
       <c r="B21" s="7">
@@ -4912,7 +4918,7 @@
       <c r="F21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="15">
         <v>24</v>
       </c>
       <c r="H21" t="s">
@@ -5399,7 +5405,7 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="14" t="s">
         <v>276</v>
       </c>
       <c r="B29" s="7">
@@ -5418,7 +5424,7 @@
       <c r="F29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <v>24</v>
       </c>
       <c r="H29" t="s">
@@ -5710,7 +5716,7 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="14" t="s">
         <v>286</v>
       </c>
       <c r="B34" s="7">
@@ -5729,7 +5735,7 @@
       <c r="F34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="15">
         <v>24</v>
       </c>
       <c r="H34" t="s">
@@ -6019,7 +6025,7 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>294</v>
       </c>
       <c r="B2" s="7">
@@ -6080,7 +6086,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>302</v>
       </c>
       <c r="B3" s="7">
@@ -6144,7 +6150,7 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="12" t="s">
         <v>307</v>
       </c>
       <c r="B4" s="7">
@@ -6211,7 +6217,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="12" t="s">
         <v>312</v>
       </c>
       <c r="B5" s="7">
@@ -6336,7 +6342,7 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>317</v>
       </c>
       <c r="B7" s="7">
@@ -6400,7 +6406,7 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B8" s="7">
@@ -6461,7 +6467,7 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="12" t="s">
         <v>323</v>
       </c>
       <c r="B9" s="7">
@@ -6525,7 +6531,7 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="12" t="s">
         <v>326</v>
       </c>
       <c r="B10" s="7">
@@ -6589,7 +6595,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="12" t="s">
         <v>330</v>
       </c>
       <c r="B11" s="7">
@@ -6656,7 +6662,7 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="12" t="s">
         <v>334</v>
       </c>
       <c r="B12" s="7">
@@ -6720,7 +6726,7 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="12" t="s">
         <v>339</v>
       </c>
       <c r="B13" s="7">
@@ -6784,7 +6790,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="12" t="s">
         <v>342</v>
       </c>
       <c r="B14" s="7">
@@ -6848,7 +6854,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="12" t="s">
         <v>349</v>
       </c>
       <c r="B15" s="7">
@@ -6909,7 +6915,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="12" t="s">
         <v>352</v>
       </c>
       <c r="B16" s="7">
@@ -6976,7 +6982,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="12" t="s">
         <v>356</v>
       </c>
       <c r="B17" s="7">
@@ -7040,7 +7046,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="12" t="s">
         <v>360</v>
       </c>
       <c r="B18" s="7">
@@ -7104,7 +7110,7 @@
       </c>
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="12" t="s">
         <v>363</v>
       </c>
       <c r="B19" s="7">
@@ -7168,7 +7174,7 @@
       </c>
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="12" t="s">
         <v>368</v>
       </c>
       <c r="B20" s="7">
@@ -7293,7 +7299,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="12" t="s">
         <v>110</v>
       </c>
       <c r="B22" s="7">
@@ -7357,7 +7363,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="12" t="s">
         <v>372</v>
       </c>
       <c r="B23" s="7">
@@ -7421,7 +7427,7 @@
       </c>
     </row>
     <row r="24" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="12" t="s">
         <v>375</v>
       </c>
       <c r="B24" s="7">
@@ -7482,7 +7488,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="12" t="s">
         <v>118</v>
       </c>
       <c r="B25" s="7">
@@ -7543,7 +7549,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="12" t="s">
         <v>378</v>
       </c>
       <c r="B26" s="7">
@@ -7610,7 +7616,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="12" t="s">
         <v>381</v>
       </c>
       <c r="B27" s="7">
@@ -7674,7 +7680,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="12" t="s">
         <v>383</v>
       </c>
       <c r="B28" s="7">
@@ -7735,7 +7741,7 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="12" t="s">
         <v>387</v>
       </c>
       <c r="B29" s="7">
@@ -7802,7 +7808,7 @@
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="12" t="s">
         <v>133</v>
       </c>
       <c r="B30" s="7">
@@ -7930,7 +7936,7 @@
       </c>
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="12" t="s">
         <v>392</v>
       </c>
       <c r="B32" s="7">
@@ -8160,7 +8166,7 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>395</v>
       </c>
       <c r="B2" s="7">
@@ -8227,7 +8233,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>403</v>
       </c>
       <c r="B3" s="7">

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A6D635-DB05-4247-BB21-65890416DC9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F650DFA-CD6A-4EAF-BEA5-DFEF3617B2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -1406,7 +1406,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1423,12 +1423,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF33CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1468,7 +1462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1483,18 +1477,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3942,7 +3933,7 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>177</v>
       </c>
       <c r="B6" s="7">
@@ -4003,7 +3994,7 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>182</v>
       </c>
       <c r="B7" s="7">
@@ -4070,7 +4061,7 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>187</v>
       </c>
       <c r="B8" s="7">
@@ -4134,7 +4125,7 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>192</v>
       </c>
       <c r="B9" s="7">
@@ -4198,7 +4189,7 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>198</v>
       </c>
       <c r="B10" s="7">
@@ -4265,7 +4256,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>204</v>
       </c>
       <c r="B11" s="7">
@@ -4329,7 +4320,7 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>207</v>
       </c>
       <c r="B12" s="7">
@@ -4393,7 +4384,7 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>213</v>
       </c>
       <c r="B13" s="7">
@@ -4457,7 +4448,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>218</v>
       </c>
       <c r="B14" s="7">
@@ -4521,7 +4512,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>223</v>
       </c>
       <c r="B15" s="7">
@@ -4582,7 +4573,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>229</v>
       </c>
       <c r="B16" s="7">
@@ -4643,7 +4634,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>231</v>
       </c>
       <c r="B17" s="7">
@@ -4707,7 +4698,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>235</v>
       </c>
       <c r="B18" s="7">
@@ -4771,7 +4762,7 @@
       </c>
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>239</v>
       </c>
       <c r="B19" s="7">
@@ -4835,7 +4826,7 @@
       </c>
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>245</v>
       </c>
       <c r="B20" s="7">
@@ -4899,7 +4890,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>250</v>
       </c>
       <c r="B21" s="7">
@@ -4909,7 +4900,7 @@
         <f t="shared" si="0"/>
         <v>Friday</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="12" t="s">
         <v>251</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -4918,7 +4909,7 @@
       <c r="F21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="14">
         <v>24</v>
       </c>
       <c r="H21" t="s">
@@ -4960,7 +4951,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>254</v>
       </c>
       <c r="B22" s="7">
@@ -5027,7 +5018,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>258</v>
       </c>
       <c r="B23" s="7">
@@ -5091,7 +5082,7 @@
       </c>
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>263</v>
       </c>
       <c r="B24" s="7">
@@ -5155,7 +5146,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="11" t="s">
         <v>267</v>
       </c>
       <c r="B25" s="7">
@@ -5216,7 +5207,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>269</v>
       </c>
       <c r="B26" s="7">
@@ -5277,7 +5268,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="11" t="s">
         <v>271</v>
       </c>
       <c r="B27" s="7">
@@ -5341,7 +5332,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="11" t="s">
         <v>273</v>
       </c>
       <c r="B28" s="7">
@@ -5405,7 +5396,7 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="13" t="s">
         <v>276</v>
       </c>
       <c r="B29" s="7">
@@ -5415,7 +5406,7 @@
         <f t="shared" si="0"/>
         <v>Friday</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="12" t="s">
         <v>251</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -5424,7 +5415,7 @@
       <c r="F29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="14">
         <v>24</v>
       </c>
       <c r="H29" t="s">
@@ -5466,7 +5457,7 @@
       </c>
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>278</v>
       </c>
       <c r="B30" s="7">
@@ -5530,7 +5521,7 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="11" t="s">
         <v>281</v>
       </c>
       <c r="B31" s="7">
@@ -5716,7 +5707,7 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="13" t="s">
         <v>286</v>
       </c>
       <c r="B34" s="7">
@@ -5726,7 +5717,7 @@
         <f t="shared" si="0"/>
         <v>Friday</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="12" t="s">
         <v>251</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -5735,7 +5726,7 @@
       <c r="F34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="14">
         <v>24</v>
       </c>
       <c r="H34" t="s">
@@ -5777,7 +5768,7 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="11" t="s">
         <v>288</v>
       </c>
       <c r="B35" s="7">
@@ -5844,7 +5835,7 @@
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="11" t="s">
         <v>290</v>
       </c>
       <c r="B36" s="7">
@@ -6025,7 +6016,7 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B2" s="7">
@@ -6068,7 +6059,7 @@
       <c r="O2" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="10" t="s">
         <v>300</v>
       </c>
       <c r="R2" t="s">
@@ -6086,7 +6077,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>302</v>
       </c>
       <c r="B3" s="7">
@@ -6132,7 +6123,7 @@
       <c r="P3" t="s">
         <v>242</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="10" t="s">
         <v>305</v>
       </c>
       <c r="R3" t="s">
@@ -6150,7 +6141,7 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>307</v>
       </c>
       <c r="B4" s="7">
@@ -6199,7 +6190,7 @@
       <c r="P4" t="s">
         <v>147</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="10" t="s">
         <v>311</v>
       </c>
       <c r="R4" t="s">
@@ -6217,7 +6208,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B5" s="7">
@@ -6327,7 +6318,7 @@
       <c r="P6" t="s">
         <v>215</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="10" t="s">
         <v>216</v>
       </c>
       <c r="S6" t="s">
@@ -6342,7 +6333,7 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>317</v>
       </c>
       <c r="B7" s="7">
@@ -6388,7 +6379,7 @@
       <c r="P7" t="s">
         <v>232</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="10" t="s">
         <v>319</v>
       </c>
       <c r="R7" t="s">
@@ -6406,7 +6397,7 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>154</v>
       </c>
       <c r="B8" s="7">
@@ -6449,7 +6440,7 @@
       <c r="O8" t="s">
         <v>29</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="10" t="s">
         <v>322</v>
       </c>
       <c r="R8" t="s">
@@ -6467,7 +6458,7 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>323</v>
       </c>
       <c r="B9" s="7">
@@ -6513,7 +6504,7 @@
       <c r="O9" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="Q9" s="10" t="s">
         <v>325</v>
       </c>
       <c r="R9" t="s">
@@ -6531,7 +6522,7 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>326</v>
       </c>
       <c r="B10" s="7">
@@ -6577,7 +6568,7 @@
       <c r="P10" t="s">
         <v>247</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="10" t="s">
         <v>328</v>
       </c>
       <c r="R10" t="s">
@@ -6595,7 +6586,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>330</v>
       </c>
       <c r="B11" s="7">
@@ -6644,7 +6635,7 @@
       <c r="P11" t="s">
         <v>55</v>
       </c>
-      <c r="Q11" s="11" t="s">
+      <c r="Q11" s="10" t="s">
         <v>332</v>
       </c>
       <c r="R11" t="s">
@@ -6662,7 +6653,7 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>334</v>
       </c>
       <c r="B12" s="7">
@@ -6708,7 +6699,7 @@
       <c r="O12" t="s">
         <v>29</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="10" t="s">
         <v>337</v>
       </c>
       <c r="R12" t="s">
@@ -6726,7 +6717,7 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>339</v>
       </c>
       <c r="B13" s="7">
@@ -6772,7 +6763,7 @@
       <c r="O13" t="s">
         <v>29</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="10" t="s">
         <v>340</v>
       </c>
       <c r="R13" t="s">
@@ -6790,7 +6781,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>342</v>
       </c>
       <c r="B14" s="7">
@@ -6836,7 +6827,7 @@
       <c r="P14" t="s">
         <v>346</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="10" t="s">
         <v>347</v>
       </c>
       <c r="R14" t="s">
@@ -6854,7 +6845,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>349</v>
       </c>
       <c r="B15" s="7">
@@ -6897,7 +6888,7 @@
       <c r="O15" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="Q15" s="10" t="s">
         <v>351</v>
       </c>
       <c r="R15" t="s">
@@ -6915,7 +6906,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>352</v>
       </c>
       <c r="B16" s="7">
@@ -6964,7 +6955,7 @@
       <c r="P16" t="s">
         <v>101</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="Q16" s="10" t="s">
         <v>354</v>
       </c>
       <c r="R16" t="s">
@@ -6982,7 +6973,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>356</v>
       </c>
       <c r="B17" s="7">
@@ -7028,7 +7019,7 @@
       <c r="P17" t="s">
         <v>357</v>
       </c>
-      <c r="Q17" s="11" t="s">
+      <c r="Q17" s="10" t="s">
         <v>358</v>
       </c>
       <c r="R17" t="s">
@@ -7046,7 +7037,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>360</v>
       </c>
       <c r="B18" s="7">
@@ -7092,7 +7083,7 @@
       <c r="O18" t="s">
         <v>29</v>
       </c>
-      <c r="Q18" s="11" t="s">
+      <c r="Q18" s="10" t="s">
         <v>362</v>
       </c>
       <c r="R18" t="s">
@@ -7110,7 +7101,7 @@
       </c>
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>363</v>
       </c>
       <c r="B19" s="7">
@@ -7174,7 +7165,7 @@
       </c>
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>368</v>
       </c>
       <c r="B20" s="7">
@@ -7217,7 +7208,7 @@
       <c r="O20" t="s">
         <v>29</v>
       </c>
-      <c r="Q20" s="11" t="s">
+      <c r="Q20" s="10" t="s">
         <v>369</v>
       </c>
       <c r="R20" t="s">
@@ -7299,7 +7290,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>110</v>
       </c>
       <c r="B22" s="7">
@@ -7345,7 +7336,7 @@
       <c r="P22" t="s">
         <v>112</v>
       </c>
-      <c r="Q22" s="11" t="s">
+      <c r="Q22" s="10" t="s">
         <v>371</v>
       </c>
       <c r="R22" t="s">
@@ -7363,7 +7354,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>372</v>
       </c>
       <c r="B23" s="7">
@@ -7409,7 +7400,7 @@
       <c r="O23" t="s">
         <v>29</v>
       </c>
-      <c r="Q23" s="11" t="s">
+      <c r="Q23" s="10" t="s">
         <v>374</v>
       </c>
       <c r="R23" t="s">
@@ -7427,7 +7418,7 @@
       </c>
     </row>
     <row r="24" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>375</v>
       </c>
       <c r="B24" s="7">
@@ -7470,7 +7461,7 @@
       <c r="O24" t="s">
         <v>29</v>
       </c>
-      <c r="Q24" s="11" t="s">
+      <c r="Q24" s="10" t="s">
         <v>376</v>
       </c>
       <c r="R24" t="s">
@@ -7488,7 +7479,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B25" s="7">
@@ -7531,7 +7522,7 @@
       <c r="O25" t="s">
         <v>29</v>
       </c>
-      <c r="Q25" s="11" t="s">
+      <c r="Q25" s="10" t="s">
         <v>377</v>
       </c>
       <c r="R25" t="s">
@@ -7549,7 +7540,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>378</v>
       </c>
       <c r="B26" s="7">
@@ -7598,7 +7589,7 @@
       <c r="P26" t="s">
         <v>201</v>
       </c>
-      <c r="Q26" s="11" t="s">
+      <c r="Q26" s="10" t="s">
         <v>380</v>
       </c>
       <c r="R26" t="s">
@@ -7616,7 +7607,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="11" t="s">
         <v>381</v>
       </c>
       <c r="B27" s="7">
@@ -7662,7 +7653,7 @@
       <c r="P27" t="s">
         <v>215</v>
       </c>
-      <c r="Q27" s="11" t="s">
+      <c r="Q27" s="10" t="s">
         <v>382</v>
       </c>
       <c r="R27" t="s">
@@ -7680,7 +7671,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="11" t="s">
         <v>383</v>
       </c>
       <c r="B28" s="7">
@@ -7723,7 +7714,7 @@
       <c r="O28" t="s">
         <v>29</v>
       </c>
-      <c r="Q28" s="11" t="s">
+      <c r="Q28" s="10" t="s">
         <v>385</v>
       </c>
       <c r="R28" t="s">
@@ -7741,7 +7732,7 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="11" t="s">
         <v>387</v>
       </c>
       <c r="B29" s="7">
@@ -7790,7 +7781,7 @@
       <c r="P29" t="s">
         <v>55</v>
       </c>
-      <c r="Q29" s="11" t="s">
+      <c r="Q29" s="10" t="s">
         <v>388</v>
       </c>
       <c r="R29" t="s">
@@ -7808,7 +7799,7 @@
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>133</v>
       </c>
       <c r="B30" s="7">
@@ -7854,7 +7845,7 @@
       <c r="P30" t="s">
         <v>136</v>
       </c>
-      <c r="Q30" s="11" t="s">
+      <c r="Q30" s="10" t="s">
         <v>390</v>
       </c>
       <c r="R30" t="s">
@@ -7936,7 +7927,7 @@
       </c>
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>392</v>
       </c>
       <c r="B32" s="7">
@@ -7979,7 +7970,7 @@
       <c r="O32" t="s">
         <v>29</v>
       </c>
-      <c r="Q32" s="11" t="s">
+      <c r="Q32" s="10" t="s">
         <v>393</v>
       </c>
       <c r="R32" t="s">
@@ -8166,7 +8157,7 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>395</v>
       </c>
       <c r="B2" s="7">
@@ -8215,7 +8206,7 @@
       <c r="P2" t="s">
         <v>101</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="10" t="s">
         <v>401</v>
       </c>
       <c r="R2" t="s">
@@ -8233,7 +8224,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>403</v>
       </c>
       <c r="B3" s="7">
@@ -8282,7 +8273,7 @@
       <c r="P3" t="s">
         <v>147</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="10" t="s">
         <v>406</v>
       </c>
       <c r="R3" t="s">
@@ -8300,7 +8291,7 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>407</v>
       </c>
       <c r="B4" s="7">
@@ -8346,7 +8337,7 @@
       <c r="P4" t="s">
         <v>210</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="10" t="s">
         <v>409</v>
       </c>
       <c r="R4" t="s">
@@ -8364,7 +8355,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>411</v>
       </c>
       <c r="B5" s="7">
@@ -8410,7 +8401,7 @@
       <c r="O5" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="Q5" s="10" t="s">
         <v>414</v>
       </c>
       <c r="R5" t="s">
@@ -8474,7 +8465,7 @@
       <c r="P6" t="s">
         <v>215</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="10" t="s">
         <v>382</v>
       </c>
       <c r="S6" t="s">
@@ -8489,7 +8480,7 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
         <v>416</v>
       </c>
       <c r="B7" s="7">
@@ -8535,7 +8526,7 @@
       <c r="P7" t="s">
         <v>247</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="10" t="s">
         <v>417</v>
       </c>
       <c r="R7" t="s">
@@ -8553,7 +8544,7 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="11" t="s">
         <v>419</v>
       </c>
       <c r="B8" s="7">
@@ -8617,7 +8608,7 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>422</v>
       </c>
       <c r="B9" s="7">
@@ -8660,7 +8651,7 @@
       <c r="O9" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="Q9" s="10" t="s">
         <v>424</v>
       </c>
       <c r="R9" t="s">
@@ -8678,7 +8669,7 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>425</v>
       </c>
       <c r="B10" s="7">
@@ -8724,7 +8715,7 @@
       <c r="O10" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="10" t="s">
         <v>427</v>
       </c>
       <c r="R10" t="s">
@@ -8742,7 +8733,7 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>428</v>
       </c>
       <c r="B11" s="7">
@@ -8788,7 +8779,7 @@
       <c r="P11" t="s">
         <v>112</v>
       </c>
-      <c r="Q11" s="11" t="s">
+      <c r="Q11" s="10" t="s">
         <v>430</v>
       </c>
       <c r="R11" t="s">
@@ -8852,7 +8843,7 @@
       <c r="P12" t="s">
         <v>247</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="10" t="s">
         <v>417</v>
       </c>
       <c r="S12" t="s">
@@ -8913,7 +8904,7 @@
       <c r="P13" t="s">
         <v>215</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="10" t="s">
         <v>382</v>
       </c>
       <c r="S13" t="s">
@@ -8928,7 +8919,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>204</v>
       </c>
       <c r="B14" s="7">
@@ -8974,7 +8965,7 @@
       <c r="P14" t="s">
         <v>112</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="10" t="s">
         <v>434</v>
       </c>
       <c r="R14" t="s">
@@ -9038,7 +9029,7 @@
       <c r="P15" t="s">
         <v>247</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="Q15" s="10" t="s">
         <v>417</v>
       </c>
       <c r="S15" t="s">
@@ -9053,7 +9044,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>436</v>
       </c>
       <c r="B16" s="7">
@@ -9102,7 +9093,7 @@
       <c r="P16" t="s">
         <v>438</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="Q16" s="10" t="s">
         <v>439</v>
       </c>
       <c r="R16" t="s">

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F650DFA-CD6A-4EAF-BEA5-DFEF3617B2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74858F10-B55B-4F88-A1E2-D2163A6A5F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="441">
   <si>
     <t>Event Name</t>
   </si>
@@ -1988,6 +1988,9 @@
       <c r="M2" t="s">
         <v>23</v>
       </c>
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
       <c r="O2" t="s">
         <v>29</v>
       </c>
@@ -2113,6 +2116,9 @@
       <c r="M4" t="s">
         <v>46</v>
       </c>
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
       <c r="O4" t="s">
         <v>29</v>
       </c>
@@ -2238,6 +2244,9 @@
       <c r="M6" t="s">
         <v>23</v>
       </c>
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
       <c r="O6" t="s">
         <v>29</v>
       </c>
@@ -2363,6 +2372,9 @@
       <c r="M8" t="s">
         <v>23</v>
       </c>
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
       <c r="O8" t="s">
         <v>29</v>
       </c>
@@ -2421,6 +2433,9 @@
       <c r="M9" t="s">
         <v>75</v>
       </c>
+      <c r="N9" t="s">
+        <v>41</v>
+      </c>
       <c r="O9" t="s">
         <v>29</v>
       </c>
@@ -2866,6 +2881,9 @@
       <c r="M16" t="s">
         <v>99</v>
       </c>
+      <c r="N16" t="s">
+        <v>29</v>
+      </c>
       <c r="O16" t="s">
         <v>29</v>
       </c>
@@ -3114,7 +3132,7 @@
         <v>86</v>
       </c>
       <c r="N20" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="O20" t="s">
         <v>41</v>
@@ -3238,6 +3256,9 @@
       <c r="L22" t="s">
         <v>142</v>
       </c>
+      <c r="N22" t="s">
+        <v>41</v>
+      </c>
       <c r="O22" t="s">
         <v>29</v>
       </c>
@@ -3295,6 +3316,9 @@
       </c>
       <c r="M23" t="s">
         <v>99</v>
+      </c>
+      <c r="N23" t="s">
+        <v>29</v>
       </c>
       <c r="O23" t="s">
         <v>41</v>
@@ -3732,6 +3756,9 @@
       <c r="M2" t="s">
         <v>23</v>
       </c>
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
       <c r="O2" t="s">
         <v>29</v>
       </c>
@@ -3791,7 +3818,7 @@
         <v>86</v>
       </c>
       <c r="N3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="O3" t="s">
         <v>41</v>
@@ -3857,6 +3884,9 @@
       <c r="M4" t="s">
         <v>46</v>
       </c>
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
       <c r="O4" t="s">
         <v>29</v>
       </c>
@@ -3915,6 +3945,9 @@
       <c r="M5" t="s">
         <v>99</v>
       </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
       <c r="O5" t="s">
         <v>41</v>
       </c>
@@ -5246,6 +5279,9 @@
       </c>
       <c r="M26" t="s">
         <v>46</v>
+      </c>
+      <c r="N26" t="s">
+        <v>41</v>
       </c>
       <c r="O26" t="s">
         <v>29</v>
@@ -6885,6 +6921,9 @@
       <c r="M15" t="s">
         <v>46</v>
       </c>
+      <c r="N15" t="s">
+        <v>41</v>
+      </c>
       <c r="O15" t="s">
         <v>29</v>
       </c>
@@ -7264,7 +7303,7 @@
         <v>36</v>
       </c>
       <c r="N21" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="O21" t="s">
         <v>41</v>
@@ -7458,6 +7497,9 @@
       <c r="M24" t="s">
         <v>46</v>
       </c>
+      <c r="N24" t="s">
+        <v>41</v>
+      </c>
       <c r="O24" t="s">
         <v>29</v>
       </c>
@@ -7901,7 +7943,7 @@
         <v>36</v>
       </c>
       <c r="N31" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="O31" t="s">
         <v>41</v>
@@ -8648,6 +8690,9 @@
       <c r="M9" t="s">
         <v>46</v>
       </c>
+      <c r="N9" t="s">
+        <v>41</v>
+      </c>
       <c r="O9" t="s">
         <v>29</v>
       </c>

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EA4426-1A10-4C49-BAC2-8207590F5361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1BBA80-B57F-4B87-B588-795BFB7B42CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="490">
   <si>
     <t>Event Name</t>
   </si>
@@ -215,150 +215,153 @@
     <t>Explore autism in the early years through a strengths-based, neurodevelopmental and inclusive lens, developing understanding of how autistic children may experience communication, interaction, sensory processing and the early years environment, with practical strategies and environmental adaptations to promote inclusion and positive relationships.</t>
   </si>
   <si>
+    <t>October Outdoor Learning Morning for Childminders and Children</t>
+  </si>
+  <si>
+    <t>Broadmoor Lane Orchard Park. Bath</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/october-outdoor-learning-morning-for-childminders-and-children/</t>
+  </si>
+  <si>
+    <t>New to EYFS – Strengthening Early Years Teaching</t>
+  </si>
+  <si>
+    <t>9:30 am - 4:00 pm</t>
+  </si>
+  <si>
+    <t>EYFS Learning Community</t>
+  </si>
+  <si>
+    <t>AT Webinar RP1-26-27</t>
+  </si>
+  <si>
+    <t>Presenter: Anna Morgan.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/new-to-eyfs-strengthening-early-years-teaching-oct-26/</t>
+  </si>
+  <si>
+    <t>A one-day online course for Early Years Practitioners and Teachers new to the EYFS framework in schools, linked to the DfE's Best Start in Life vision. Covers the core principles of the EYFS — the four overarching themes, Characteristics of Effective Learning, Prime Areas and educational programmes — alongside observation, assessment and planning, the role of the adult, the key person approach and enabling environments that put children and families at the heart of practice.</t>
+  </si>
+  <si>
+    <t>Childminder Network: Running a Sustainable Childminding Business</t>
+  </si>
+  <si>
+    <t>6:30 pm - 8:00 pm</t>
+  </si>
+  <si>
+    <t>NW Childminders RP1-26-27</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/childminder-network-running-a-sustainable-childminding-business/</t>
+  </si>
+  <si>
+    <t>Do you struggle to know how your childminding setting is running from a business point of view? Many of us have started as a childminder with very little business experience. Come and talk about how you market and recruit new families, how you manage your finances, what sustainability looks like with new funding models and options for growing your business.</t>
+  </si>
+  <si>
+    <t>Talking With Babies</t>
+  </si>
+  <si>
+    <t>6:15 pm - 8:15 pm</t>
+  </si>
+  <si>
+    <t>Working with Babies</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/talking-with-babies-oct-2026/</t>
+  </si>
+  <si>
+    <t>This session will explore how we can talk with babies to help them become confident communicators and develop respectful relationships that enable them to make genuine choices. We will consider how mindful care routines might support communication and language, the power of nonverbal communication, and learning the ‘conversational dance’.</t>
+  </si>
+  <si>
+    <t>Bristol Terrific Twos Network Sessions - October 2026</t>
+  </si>
+  <si>
+    <t>4:00 pm - 6:00 pm</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Hartcliffe Nursery School</t>
+  </si>
+  <si>
+    <t>NW Spotlight on Twos RP1-26-27</t>
+  </si>
+  <si>
+    <t>Spotlight on Twos</t>
+  </si>
+  <si>
+    <t>Hosted by Hartcliffe Nursery School. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
+  </si>
+  <si>
+    <t>https://calendar.bristolearlyyears.org.uk/</t>
+  </si>
+  <si>
+    <t>The Terrific Twos Network is an opportunity for early years practitioners and leaders in Bristol to connect around a shared passion for working with two-year-olds. Whether experienced or new to the age group, and whether based in a setting, school or childminder provision, this is a chance to focus on this unique age group, visit other settings and gain peer support. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
+  </si>
+  <si>
+    <t>External</t>
+  </si>
+  <si>
+    <t>How Can a Playful Pedagogy Work Within a Home-Based Childcare Setting? With Michelle Malamo</t>
+  </si>
+  <si>
+    <t>PD PSED RP1-26-27</t>
+  </si>
+  <si>
+    <t>Presenter: Michelle Malamo. Can record.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/how-can-a-playful-pedagogy-work-within-a-home-based-childcare-setting-with-michelle-malamo/</t>
+  </si>
+  <si>
+    <t>A webinar for childminders exploring playful, therapeutic practices that meet the needs of babies and young children through play, considering how different types of play, flexible play environments and intentional adult responses support children's development, wellbeing and learning. Participants will reflect on embedding playful pedagogy within home-based childcare settings and leave with practical strategies to implement immediately.</t>
+  </si>
+  <si>
+    <t>CPD Programme: Using Evidence to Strengthen Your Early Years Leadership - Session 1</t>
+  </si>
+  <si>
+    <t>9:00 am - 12:00 pm</t>
+  </si>
+  <si>
+    <t>St Pauls Nursery Community Room</t>
+  </si>
+  <si>
+    <t>Leadership</t>
+  </si>
+  <si>
+    <t>Presenters: Tom Colquhoun and Lucy Driver. Delivered in collaboration with the Somerset Research School.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/cpd-programme-using-evidence-to-strengthen-your-early-years-leadership-2026/</t>
+  </si>
+  <si>
+    <t>A three-part face-to-face leadership programme delivered in collaboration with the Somerset Research School, for Headteachers, EYFS Leads, Nursery/Pre-School Managers, Room Leaders and EYFS Teachers. The programme supports those leading in the early years to engage with the growing body of educational research evidence and use it to make decisions about the 'best bets' for their school or setting.</t>
+  </si>
+  <si>
     <t>Bristol Baby Practitioner Clusters - October 2026</t>
   </si>
   <si>
     <t>6:15 pm - 7:45 pm</t>
   </si>
   <si>
-    <t>Local</t>
-  </si>
-  <si>
     <t>Partou Little Big Steps</t>
   </si>
   <si>
     <t>NW Working with Babies RP1-26-27</t>
   </si>
   <si>
-    <t>Working with Babies</t>
-  </si>
-  <si>
     <t>Hosted by Partou Little Big Steps. Facilitators: Bev Roberts (Manager), Amber O'Connor (Under Two's Unit Leader).</t>
   </si>
   <si>
-    <t>https://calendar.bristolearlyyears.org.uk/</t>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-october-2026/</t>
   </si>
   <si>
     <t>Bristol's Baby Practitioner Networks have grown from six citywide meetings to nine locality-based clusters, with three meetings each in North, South and East &amp; Central Bristol, giving practitioners more opportunities to connect, share practice and be part of a supportive community focused on giving babies the best start in life. Free to attend and open to all — explore current themes in baby room practice, share ideas and celebrate great practice.</t>
   </si>
   <si>
-    <t>External</t>
-  </si>
-  <si>
-    <t>October Outdoor Learning Morning for Childminders and Children</t>
-  </si>
-  <si>
-    <t>Broadmoor Lane Orchard Park. Bath</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/october-outdoor-learning-morning-for-childminders-and-children/</t>
-  </si>
-  <si>
-    <t>New to EYFS – Strengthening Early Years Teaching</t>
-  </si>
-  <si>
-    <t>9:30 am - 4:00 pm</t>
-  </si>
-  <si>
-    <t>EYFS Learning Community</t>
-  </si>
-  <si>
-    <t>AT Webinar RP1-26-27</t>
-  </si>
-  <si>
-    <t>Presenter: Anna Morgan.</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/new-to-eyfs-strengthening-early-years-teaching-oct-26/</t>
-  </si>
-  <si>
-    <t>A one-day online course for Early Years Practitioners and Teachers new to the EYFS framework in schools, linked to the DfE's Best Start in Life vision. Covers the core principles of the EYFS — the four overarching themes, Characteristics of Effective Learning, Prime Areas and educational programmes — alongside observation, assessment and planning, the role of the adult, the key person approach and enabling environments that put children and families at the heart of practice.</t>
-  </si>
-  <si>
-    <t>Childminder Network: Running a Sustainable Childminding Business</t>
-  </si>
-  <si>
-    <t>6:30 pm - 8:00 pm</t>
-  </si>
-  <si>
-    <t>NW Childminders RP1-26-27</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/childminder-network-running-a-sustainable-childminding-business/</t>
-  </si>
-  <si>
-    <t>Do you struggle to know how your childminding setting is running from a business point of view? Many of us have started as a childminder with very little business experience. Come and talk about how you market and recruit new families, how you manage your finances, what sustainability looks like with new funding models and options for growing your business.</t>
-  </si>
-  <si>
-    <t>Talking With Babies</t>
-  </si>
-  <si>
-    <t>6:15 pm - 8:15 pm</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/talking-with-babies-oct-2026/</t>
-  </si>
-  <si>
-    <t>This session will explore how we can talk with babies to help them become confident communicators and develop respectful relationships that enable them to make genuine choices. We will consider how mindful care routines might support communication and language, the power of nonverbal communication, and learning the ‘conversational dance’.</t>
-  </si>
-  <si>
-    <t>Bristol Twos Network - October 2026</t>
-  </si>
-  <si>
-    <t>4:00 pm - 6:00 pm</t>
-  </si>
-  <si>
-    <t>Hartcliffe Nursery School</t>
-  </si>
-  <si>
-    <t>NW Spotlight on Twos RP1-26-27</t>
-  </si>
-  <si>
-    <t>Spotlight on Twos</t>
-  </si>
-  <si>
-    <t>Hosted by Hartcliffe Nursery School. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
-  </si>
-  <si>
-    <t>The Terrific Twos Network is an opportunity for early years practitioners and leaders in Bristol to connect around a shared passion for working with two-year-olds. Whether experienced or new to the age group, and whether based in a setting, school or childminder provision, this is a chance to focus on this unique age group, visit other settings and gain peer support. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
-  </si>
-  <si>
-    <t>How Can a Playful Pedagogy Work Within a Home-Based Childcare Setting? With Michelle Malamo</t>
-  </si>
-  <si>
-    <t>PD PSED RP1-26-27</t>
-  </si>
-  <si>
-    <t>Presenter: Michelle Malamo. Can record.</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/how-can-a-playful-pedagogy-work-within-a-home-based-childcare-setting-with-michelle-malamo/</t>
-  </si>
-  <si>
-    <t>A webinar for childminders exploring playful, therapeutic practices that meet the needs of babies and young children through play, considering how different types of play, flexible play environments and intentional adult responses support children's development, wellbeing and learning. Participants will reflect on embedding playful pedagogy within home-based childcare settings and leave with practical strategies to implement immediately.</t>
-  </si>
-  <si>
-    <t>CPD Programme: Using Evidence to Strengthen Your Early Years Leadership - Session 1</t>
-  </si>
-  <si>
-    <t>9:00 am - 12:00 pm</t>
-  </si>
-  <si>
-    <t>St Pauls Nursery Community Room</t>
-  </si>
-  <si>
-    <t>Leadership</t>
-  </si>
-  <si>
-    <t>Presenters: Tom Colquhoun and Lucy Driver. Delivered in collaboration with the Somerset Research School.</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/cpd-programme-using-evidence-to-strengthen-your-early-years-leadership-2026/</t>
-  </si>
-  <si>
-    <t>A three-part face-to-face leadership programme delivered in collaboration with the Somerset Research School, for Headteachers, EYFS Leads, Nursery/Pre-School Managers, Room Leaders and EYFS Teachers. The programme supports those leading in the early years to engage with the growing body of educational research evidence and use it to make decisions about the 'best bets' for their school or setting.</t>
-  </si>
-  <si>
     <t>Mathematising the Day</t>
   </si>
   <si>
@@ -680,7 +683,7 @@
     <t>Explore how childminders can transform ordinary home environments into rich movement spaces that support children's physical development, confidence, wellbeing and learning, drawing on current research in this practical, interactive webinar.</t>
   </si>
   <si>
-    <t>Bristol Twos Network - December 2026</t>
+    <t>Bristol Terrific Twos Network Sessions - December 2026</t>
   </si>
   <si>
     <t>6:00 pm - 8:00 pm</t>
@@ -971,7 +974,7 @@
     <t>https://beyth.co.uk/course/maths-network-february-2027/</t>
   </si>
   <si>
-    <t>Bristol Twos Network - February 2027</t>
+    <t>Bristol Terrific Twos Network Sessions - February 2027</t>
   </si>
   <si>
     <t>Snapdragons Horfield</t>
@@ -1070,7 +1073,7 @@
     <t>Explore how to create maths-rich environments filled with challenging tasks and interesting mathematical tools, exploring the Firm Foundations of Early Maths and how continuous provision can be carefully prepared to support children's early maths learning, both indoors and out.</t>
   </si>
   <si>
-    <t>Bristol Twos Network - March 2027</t>
+    <t>Bristol Terrific Twos Network Sessions - March 2027</t>
   </si>
   <si>
     <t>4:30 pm - 6:30 pm</t>
@@ -1310,7 +1313,7 @@
     <t>EAL in the Early Years – Unlocking the Potential of Every Child (CPD Programme) - Session 3</t>
   </si>
   <si>
-    <t>Bristol Twos Network - May 2027</t>
+    <t>Bristol Terrific Twos Network Sessions - May 2027</t>
   </si>
   <si>
     <t>5:00 pm - 7:00 pm</t>
@@ -1472,7 +1475,7 @@
     <t>https://beyth.co.uk/course/learning-through-a-continuous-provision-approach-july-27/</t>
   </si>
   <si>
-    <t>Bristol Twos Network - July 2027</t>
+    <t>Bristol Terrific Twos Network Sessions - July 2027</t>
   </si>
   <si>
     <t>The Limes Nursery School</t>
@@ -1503,6 +1506,9 @@
   </si>
   <si>
     <t>Join Specialist Health Visitor Sarah Clarke to explore infant mental health and wellbeing and how it shapes babies' current and lifelong development, sharing ideas to support babies' mental health and development in early years settings — part of the Talking About... series of informal online networking sessions.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-october-2026/</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1545,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1570,6 +1576,18 @@
         <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1580,11 +1598,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1595,20 +1612,23 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2310,7 +2330,7 @@
       <c r="P5" t="s">
         <v>55</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="8" t="s">
         <v>56</v>
       </c>
       <c r="R5" t="s">
@@ -2328,27 +2348,27 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B6" s="7">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Thursday</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="G6" s="2">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
         <v>25</v>
@@ -2357,37 +2377,31 @@
         <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="K6" t="s">
         <v>28</v>
       </c>
-      <c r="L6" t="s">
-        <v>62</v>
-      </c>
       <c r="M6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
         <v>29</v>
       </c>
       <c r="O6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R6" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="S6" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="T6" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="U6" t="b">
         <f>FALSE()</f>
@@ -2396,26 +2410,26 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B7" s="7">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="C7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Monday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
@@ -2424,13 +2438,13 @@
         <v>26</v>
       </c>
       <c r="J7" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="K7" t="s">
         <v>28</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -2438,11 +2452,14 @@
       <c r="O7" t="s">
         <v>30</v>
       </c>
+      <c r="P7" t="s">
+        <v>65</v>
+      </c>
       <c r="Q7" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R7" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -2457,26 +2474,26 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B8" s="7">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Monday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H8" t="s">
         <v>25</v>
@@ -2485,13 +2502,16 @@
         <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="K8" t="s">
         <v>28</v>
       </c>
+      <c r="L8" t="s">
+        <v>70</v>
+      </c>
       <c r="M8" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="N8" t="s">
         <v>29</v>
@@ -2499,14 +2519,11 @@
       <c r="O8" t="s">
         <v>30</v>
       </c>
-      <c r="P8" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>76</v>
+      <c r="Q8" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="R8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -2521,26 +2538,26 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B9" s="7">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Tuesday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
         <v>25</v>
@@ -2549,16 +2566,13 @@
         <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="K9" t="s">
         <v>28</v>
       </c>
-      <c r="L9" t="s">
-        <v>80</v>
-      </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -2567,10 +2581,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="R9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -2584,8 +2598,8 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>83</v>
+      <c r="A10" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="B10" s="7">
         <v>46309</v>
@@ -2595,13 +2609,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="G10" s="2">
         <v>80</v>
@@ -2613,31 +2627,37 @@
         <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="K10" t="s">
         <v>28</v>
       </c>
+      <c r="L10" t="s">
+        <v>82</v>
+      </c>
       <c r="M10" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="P10" t="s">
+        <v>84</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>85</v>
+        <v>489</v>
       </c>
       <c r="R10" t="s">
         <v>86</v>
       </c>
       <c r="S10" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="T10" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="U10" t="b">
         <f>FALSE()</f>
@@ -2645,24 +2665,24 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>87</v>
+      <c r="A11" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="B11" s="7">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="C11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="G11" s="2">
         <v>80</v>
@@ -2674,37 +2694,34 @@
         <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="K11" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" t="s">
         <v>90</v>
       </c>
-      <c r="M11" t="s">
+      <c r="Q11" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="N11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" t="s">
-        <v>29</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
         <v>92</v>
       </c>
-      <c r="Q11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="R11" t="s">
-        <v>93</v>
-      </c>
       <c r="S11" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="T11" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="U11" t="b">
         <f>FALSE()</f>
@@ -2713,7 +2730,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B12" s="7">
         <v>46315</v>
@@ -2723,16 +2740,16 @@
         <v>Tuesday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="G12" s="2">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
         <v>25</v>
@@ -2741,28 +2758,28 @@
         <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="K12" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="N12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O12" t="s">
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q12" s="9" t="s">
         <v>97</v>
       </c>
+      <c r="Q12" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="R12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -2776,27 +2793,27 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>99</v>
+      <c r="A13" s="14" t="s">
+        <v>100</v>
       </c>
       <c r="B13" s="7">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Tuesday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>101</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" s="2">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s">
         <v>25</v>
@@ -2805,34 +2822,37 @@
         <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K13" t="s">
         <v>28</v>
       </c>
+      <c r="L13" t="s">
+        <v>103</v>
+      </c>
       <c r="M13" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="N13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q13" s="9" t="s">
         <v>104</v>
       </c>
+      <c r="Q13" s="8" t="s">
+        <v>105</v>
+      </c>
       <c r="R13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S13" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="U13" t="b">
         <f>FALSE()</f>
@@ -2841,7 +2861,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B14" s="7">
         <v>46316</v>
@@ -2851,10 +2871,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -2869,14 +2889,14 @@
         <v>26</v>
       </c>
       <c r="J14" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K14" t="s">
+        <v>109</v>
+      </c>
+      <c r="M14" t="s">
         <v>108</v>
       </c>
-      <c r="M14" t="s">
-        <v>107</v>
-      </c>
       <c r="N14" t="s">
         <v>29</v>
       </c>
@@ -2884,13 +2904,13 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -2905,7 +2925,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" s="7">
         <v>46317</v>
@@ -2915,10 +2935,10 @@
         <v>Thursday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -2936,13 +2956,13 @@
         <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="L15" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="M15" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N15" t="s">
         <v>29</v>
@@ -2951,13 +2971,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q15" s="9" t="s">
         <v>115</v>
       </c>
+      <c r="Q15" s="8" t="s">
+        <v>116</v>
+      </c>
       <c r="R15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -2972,7 +2992,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" s="7">
         <v>46317</v>
@@ -2982,10 +3002,10 @@
         <v>Thursday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>38</v>
@@ -3000,13 +3020,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K16" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -3015,13 +3035,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q16" s="9" t="s">
         <v>121</v>
       </c>
+      <c r="Q16" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="R16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -3036,7 +3056,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B17" s="7">
         <v>46318</v>
@@ -3046,7 +3066,7 @@
         <v>Friday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>46</v>
@@ -3064,13 +3084,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K17" t="s">
         <v>28</v>
       </c>
       <c r="M17" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -3079,13 +3099,13 @@
         <v>30</v>
       </c>
       <c r="P17" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q17" s="9" t="s">
         <v>126</v>
       </c>
+      <c r="Q17" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="R17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -3099,8 +3119,8 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>128</v>
+      <c r="A18" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="B18" s="7">
         <v>46328</v>
@@ -3110,13 +3130,13 @@
         <v>Monday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G18" s="2">
         <v>80</v>
@@ -3134,10 +3154,10 @@
         <v>28</v>
       </c>
       <c r="L18" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="M18" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N18" t="s">
         <v>29</v>
@@ -3146,19 +3166,19 @@
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R18" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="S18" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T18" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U18" t="b">
         <f>FALSE()</f>
@@ -3167,7 +3187,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B19" s="7">
         <v>46330</v>
@@ -3177,10 +3197,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>38</v>
@@ -3195,13 +3215,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K19" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M19" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N19" t="s">
         <v>30</v>
@@ -3210,10 +3230,10 @@
         <v>30</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -3228,7 +3248,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="7">
         <v>46331</v>
@@ -3238,7 +3258,7 @@
         <v>Thursday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>37</v>
@@ -3256,7 +3276,7 @@
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K20" t="s">
         <v>40</v>
@@ -3270,11 +3290,11 @@
       <c r="O20" t="s">
         <v>30</v>
       </c>
-      <c r="Q20" s="9" t="s">
-        <v>136</v>
+      <c r="Q20" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="R20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -3289,7 +3309,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B21" s="7">
         <v>46332</v>
@@ -3299,13 +3319,13 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G21" s="2">
         <v>12</v>
@@ -3320,11 +3340,11 @@
         <v>27</v>
       </c>
       <c r="K21" t="s">
+        <v>109</v>
+      </c>
+      <c r="M21" t="s">
         <v>108</v>
       </c>
-      <c r="M21" t="s">
-        <v>107</v>
-      </c>
       <c r="N21" t="s">
         <v>29</v>
       </c>
@@ -3332,13 +3352,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -3353,7 +3373,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B22" s="7">
         <v>46335</v>
@@ -3366,7 +3386,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>38</v>
@@ -3384,25 +3404,25 @@
         <v>39</v>
       </c>
       <c r="K22" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" t="s">
         <v>145</v>
       </c>
-      <c r="M22" t="s">
-        <v>144</v>
-      </c>
       <c r="N22" t="s">
         <v>29</v>
       </c>
       <c r="O22" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" s="9" t="s">
-        <v>146</v>
+      <c r="Q22" s="8" t="s">
+        <v>147</v>
       </c>
       <c r="R22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -3417,7 +3437,7 @@
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B23" s="7">
         <v>46336</v>
@@ -3427,13 +3447,13 @@
         <v>Tuesday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2">
         <v>16</v>
@@ -3451,7 +3471,7 @@
         <v>28</v>
       </c>
       <c r="M23" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N23" t="s">
         <v>30</v>
@@ -3460,13 +3480,13 @@
         <v>29</v>
       </c>
       <c r="P23" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="R23" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -3481,7 +3501,7 @@
     </row>
     <row r="24" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B24" s="7">
         <v>46337</v>
@@ -3491,13 +3511,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2">
         <v>16</v>
@@ -3515,7 +3535,7 @@
         <v>28</v>
       </c>
       <c r="M24" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -3524,13 +3544,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q24" s="9" t="s">
         <v>152</v>
       </c>
+      <c r="Q24" s="8" t="s">
+        <v>153</v>
+      </c>
       <c r="R24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -3545,7 +3565,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B25" s="7">
         <v>46338</v>
@@ -3555,10 +3575,10 @@
         <v>Thursday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G25" s="2">
         <v>70</v>
@@ -3576,7 +3596,7 @@
         <v>28</v>
       </c>
       <c r="L25" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -3585,13 +3605,13 @@
         <v>30</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S25" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T25" t="s">
         <v>34</v>
@@ -3603,7 +3623,7 @@
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" s="7">
         <v>46344</v>
@@ -3613,10 +3633,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>38</v>
@@ -3631,13 +3651,13 @@
         <v>26</v>
       </c>
       <c r="J26" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K26" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M26" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N26" t="s">
         <v>30</v>
@@ -3646,7 +3666,7 @@
         <v>29</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -3661,7 +3681,7 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B27" s="7">
         <v>46345</v>
@@ -3707,13 +3727,13 @@
         <v>30</v>
       </c>
       <c r="P27" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q27" s="9" t="s">
         <v>161</v>
       </c>
+      <c r="Q27" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="R27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -3728,7 +3748,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B28" s="7">
         <v>46351</v>
@@ -3738,10 +3758,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -3756,13 +3776,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K28" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
@@ -3771,13 +3791,13 @@
         <v>30</v>
       </c>
       <c r="P28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="R28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S28" t="s">
         <v>33</v>
@@ -3792,7 +3812,7 @@
     </row>
     <row r="29" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B29" s="7">
         <v>46352</v>
@@ -3802,7 +3822,7 @@
         <v>Thursday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>37</v>
@@ -3820,10 +3840,10 @@
         <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="K29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s">
         <v>37</v>
@@ -3834,11 +3854,11 @@
       <c r="O29" t="s">
         <v>30</v>
       </c>
-      <c r="Q29" s="9" t="s">
-        <v>169</v>
+      <c r="Q29" s="8" t="s">
+        <v>170</v>
       </c>
       <c r="R29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -3851,9 +3871,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B30" s="7">
         <v>46352</v>
@@ -3901,11 +3921,11 @@
       <c r="P30" t="s">
         <v>55</v>
       </c>
-      <c r="Q30" s="9" t="s">
-        <v>172</v>
+      <c r="Q30" s="8" t="s">
+        <v>173</v>
       </c>
       <c r="R30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -3934,23 +3954,21 @@
     <hyperlink ref="Q3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="Q4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="Q6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="Q7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="Q8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="Q9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="Q10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="Q11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="Q14" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="Q18" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="Q19" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="Q21" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="Q23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="Q25" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="Q26" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="Q28" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="Q14" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="Q18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="Q19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="Q21" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="Q23" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="Q25" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="Q26" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="Q28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4042,7 +4060,7 @@
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B2" s="7">
         <v>46357</v>
@@ -4052,7 +4070,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
@@ -4064,19 +4082,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
@@ -4088,10 +4106,10 @@
         <v>30</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S2" t="s">
         <v>33</v>
@@ -4106,7 +4124,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B3" s="7">
         <v>46357</v>
@@ -4116,31 +4134,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2">
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N3" t="s">
         <v>30</v>
@@ -4149,13 +4167,13 @@
         <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="R3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -4169,8 +4187,8 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>184</v>
+      <c r="A4" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="B4" s="7">
         <v>46357</v>
@@ -4180,34 +4198,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2">
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M4" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -4216,19 +4234,19 @@
         <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R4" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="S4" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U4" t="b">
         <f>FALSE()</f>
@@ -4237,7 +4255,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B5" s="7">
         <v>46358</v>
@@ -4259,19 +4277,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M5" t="s">
         <v>46</v>
@@ -4283,7 +4301,7 @@
         <v>30</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R5" t="s">
         <v>49</v>
@@ -4301,7 +4319,7 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" s="7">
         <v>46358</v>
@@ -4311,10 +4329,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>38</v>
@@ -4323,19 +4341,19 @@
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N6" t="s">
         <v>30</v>
@@ -4344,7 +4362,7 @@
         <v>29</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -4359,7 +4377,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B7" s="7">
         <v>46358</v>
@@ -4369,31 +4387,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G7" s="2">
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -4401,11 +4419,11 @@
       <c r="O7" t="s">
         <v>30</v>
       </c>
-      <c r="Q7" s="9" t="s">
-        <v>196</v>
+      <c r="Q7" s="8" t="s">
+        <v>197</v>
       </c>
       <c r="R7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -4420,7 +4438,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B8" s="7">
         <v>46360</v>
@@ -4430,10 +4448,10 @@
         <v>Friday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -4442,22 +4460,22 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M8" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N8" t="s">
         <v>29</v>
@@ -4466,13 +4484,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>200</v>
+        <v>115</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="R8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -4487,7 +4505,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B9" s="7">
         <v>46363</v>
@@ -4509,19 +4527,19 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M9" t="s">
         <v>37</v>
@@ -4532,11 +4550,11 @@
       <c r="O9" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="9" t="s">
-        <v>205</v>
+      <c r="Q9" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="R9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -4551,7 +4569,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B10" s="7">
         <v>46364</v>
@@ -4561,10 +4579,10 @@
         <v>Tuesday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>38</v>
@@ -4573,20 +4591,20 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K10" t="s">
+        <v>210</v>
+      </c>
+      <c r="M10" t="s">
         <v>209</v>
       </c>
-      <c r="M10" t="s">
-        <v>208</v>
-      </c>
       <c r="N10" t="s">
         <v>29</v>
       </c>
@@ -4594,13 +4612,13 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q10" s="9" t="s">
         <v>211</v>
       </c>
+      <c r="Q10" s="8" t="s">
+        <v>212</v>
+      </c>
       <c r="R10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -4614,8 +4632,8 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>213</v>
+      <c r="A11" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="B11" s="7">
         <v>46365</v>
@@ -4625,34 +4643,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G11" s="2">
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -4661,19 +4679,19 @@
         <v>29</v>
       </c>
       <c r="P11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R11" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="S11" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T11" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U11" t="b">
         <f>FALSE()</f>
@@ -4682,7 +4700,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B12" s="7">
         <v>46366</v>
@@ -4695,7 +4713,7 @@
         <v>36</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>38</v>
@@ -4704,22 +4722,22 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -4728,13 +4746,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q12" s="9" t="s">
         <v>222</v>
       </c>
+      <c r="Q12" s="8" t="s">
+        <v>223</v>
+      </c>
       <c r="R12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -4749,7 +4767,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B13" s="7">
         <v>46394</v>
@@ -4759,7 +4777,7 @@
         <v>Thursday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>46</v>
@@ -4771,19 +4789,19 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -4792,13 +4810,13 @@
         <v>30</v>
       </c>
       <c r="P13" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>225</v>
+        <v>126</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="R13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -4813,7 +4831,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B14" s="7">
         <v>46398</v>
@@ -4823,10 +4841,10 @@
         <v>Monday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -4835,19 +4853,19 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -4856,13 +4874,13 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q14" s="9" t="s">
         <v>230</v>
       </c>
+      <c r="Q14" s="8" t="s">
+        <v>231</v>
+      </c>
       <c r="R14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -4877,7 +4895,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B15" s="7">
         <v>46400</v>
@@ -4887,10 +4905,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -4899,19 +4917,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -4920,13 +4938,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q15" s="9" t="s">
         <v>235</v>
       </c>
+      <c r="Q15" s="8" t="s">
+        <v>236</v>
+      </c>
       <c r="R15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -4941,7 +4959,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B16" s="7">
         <v>46402</v>
@@ -4951,31 +4969,31 @@
         <v>Friday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -4984,13 +5002,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q16" s="9" t="s">
         <v>240</v>
       </c>
+      <c r="Q16" s="8" t="s">
+        <v>241</v>
+      </c>
       <c r="R16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -5005,7 +5023,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B17" s="7">
         <v>46405</v>
@@ -5015,28 +5033,28 @@
         <v>Monday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G17" s="2">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M17" t="s">
         <v>52</v>
@@ -5047,11 +5065,11 @@
       <c r="O17" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="9" t="s">
-        <v>246</v>
+      <c r="Q17" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="R17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -5066,7 +5084,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B18" s="7">
         <v>46407</v>
@@ -5076,28 +5094,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G18" s="2">
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M18" t="s">
         <v>52</v>
@@ -5108,11 +5126,11 @@
       <c r="O18" t="s">
         <v>30</v>
       </c>
-      <c r="Q18" s="9" t="s">
-        <v>249</v>
+      <c r="Q18" s="8" t="s">
+        <v>250</v>
       </c>
       <c r="R18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -5127,7 +5145,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B19" s="7">
         <v>46407</v>
@@ -5137,7 +5155,7 @@
         <v>Wednesday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>46</v>
@@ -5149,19 +5167,19 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M19" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
@@ -5170,13 +5188,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -5191,7 +5209,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B20" s="7">
         <v>46408</v>
@@ -5204,7 +5222,7 @@
         <v>36</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>38</v>
@@ -5213,22 +5231,22 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
@@ -5236,11 +5254,11 @@
       <c r="O20" t="s">
         <v>30</v>
       </c>
-      <c r="Q20" s="9" t="s">
-        <v>256</v>
+      <c r="Q20" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="R20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -5255,7 +5273,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B21" s="7">
         <v>46408</v>
@@ -5265,10 +5283,10 @@
         <v>Thursday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>38</v>
@@ -5277,19 +5295,19 @@
         <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -5298,13 +5316,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q21" s="9" t="s">
         <v>261</v>
       </c>
+      <c r="Q21" s="8" t="s">
+        <v>262</v>
+      </c>
       <c r="R21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -5319,7 +5337,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B22" s="7">
         <v>46414</v>
@@ -5329,10 +5347,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>38</v>
@@ -5341,19 +5359,19 @@
         <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N22" t="s">
         <v>30</v>
@@ -5362,13 +5380,13 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q22" s="9" t="s">
         <v>266</v>
       </c>
+      <c r="Q22" s="8" t="s">
+        <v>267</v>
+      </c>
       <c r="R22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -5383,7 +5401,7 @@
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B23" s="7">
         <v>46416</v>
@@ -5393,7 +5411,7 @@
         <v>Friday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>37</v>
@@ -5405,16 +5423,16 @@
         <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M23" t="s">
         <v>37</v>
@@ -5426,10 +5444,10 @@
         <v>30</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -5444,7 +5462,7 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" s="7">
         <v>46420</v>
@@ -5454,10 +5472,10 @@
         <v>Tuesday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>38</v>
@@ -5466,22 +5484,22 @@
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L24" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -5490,13 +5508,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -5511,7 +5529,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B25" s="7">
         <v>46420</v>
@@ -5521,28 +5539,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G25" s="2">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K25" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s">
         <v>52</v>
@@ -5554,13 +5572,13 @@
         <v>30</v>
       </c>
       <c r="P25" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q25" s="9" t="s">
         <v>278</v>
       </c>
+      <c r="Q25" s="8" t="s">
+        <v>279</v>
+      </c>
       <c r="R25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -5575,7 +5593,7 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B26" s="7">
         <v>46420</v>
@@ -5585,7 +5603,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>23</v>
@@ -5597,16 +5615,16 @@
         <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -5618,13 +5636,13 @@
         <v>30</v>
       </c>
       <c r="P26" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q26" s="9" t="s">
         <v>282</v>
       </c>
+      <c r="Q26" s="8" t="s">
+        <v>283</v>
+      </c>
       <c r="R26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -5639,7 +5657,7 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B27" s="7">
         <v>46421</v>
@@ -5649,31 +5667,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G27" s="2">
         <v>12</v>
       </c>
       <c r="H27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N27" t="s">
         <v>29</v>
@@ -5681,11 +5699,11 @@
       <c r="O27" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="9" t="s">
-        <v>285</v>
+      <c r="Q27" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="R27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -5700,7 +5718,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B28" s="7">
         <v>46421</v>
@@ -5722,19 +5740,19 @@
         <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s">
         <v>46</v>
@@ -5746,7 +5764,7 @@
         <v>30</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R28" t="s">
         <v>49</v>
@@ -5764,7 +5782,7 @@
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29" s="7">
         <v>46422</v>
@@ -5774,28 +5792,28 @@
         <v>Thursday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G29" s="2">
         <v>6</v>
       </c>
       <c r="H29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s">
         <v>52</v>
@@ -5807,13 +5825,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>289</v>
+        <v>278</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="R29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -5828,7 +5846,7 @@
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" s="7">
         <v>46422</v>
@@ -5838,10 +5856,10 @@
         <v>Thursday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -5850,19 +5868,19 @@
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J30" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K30" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N30" t="s">
         <v>29</v>
@@ -5871,13 +5889,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q30" s="9" t="s">
-        <v>291</v>
+        <v>261</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>292</v>
       </c>
       <c r="R30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -5892,7 +5910,7 @@
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" s="7">
         <v>46423</v>
@@ -5902,7 +5920,7 @@
         <v>Friday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>37</v>
@@ -5914,16 +5932,16 @@
         <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M31" t="s">
         <v>37</v>
@@ -5935,10 +5953,10 @@
         <v>30</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R31" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -5953,7 +5971,7 @@
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B32" s="7">
         <v>46426</v>
@@ -5975,19 +5993,19 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M32" t="s">
         <v>37</v>
@@ -5998,11 +6016,11 @@
       <c r="O32" t="s">
         <v>30</v>
       </c>
-      <c r="Q32" s="9" t="s">
-        <v>296</v>
+      <c r="Q32" s="8" t="s">
+        <v>297</v>
       </c>
       <c r="R32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -6017,7 +6035,7 @@
     </row>
     <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B33" s="7">
         <v>46427</v>
@@ -6027,7 +6045,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>46</v>
@@ -6039,19 +6057,19 @@
         <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J33" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -6060,13 +6078,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q33" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -6080,8 +6098,8 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
-        <v>301</v>
+      <c r="A34" s="9" t="s">
+        <v>302</v>
       </c>
       <c r="B34" s="7">
         <v>46427</v>
@@ -6091,34 +6109,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G34" s="2">
         <v>80</v>
       </c>
       <c r="H34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M34" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N34" t="s">
         <v>29</v>
@@ -6127,19 +6145,19 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R34" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="S34" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T34" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U34" t="b">
         <f>FALSE()</f>
@@ -6148,7 +6166,7 @@
     </row>
     <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B35" s="7">
         <v>46428</v>
@@ -6158,10 +6176,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>38</v>
@@ -6170,19 +6188,19 @@
         <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M35" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -6191,10 +6209,10 @@
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q35" s="9" t="s">
         <v>266</v>
+      </c>
+      <c r="Q35" s="8" t="s">
+        <v>267</v>
       </c>
       <c r="S35" t="s">
         <v>33</v>
@@ -6209,7 +6227,7 @@
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B36" s="7">
         <v>46428</v>
@@ -6219,10 +6237,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>38</v>
@@ -6231,19 +6249,19 @@
         <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J36" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N36" t="s">
         <v>30</v>
@@ -6252,10 +6270,10 @@
         <v>29</v>
       </c>
       <c r="P36" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q36" s="9" t="s">
         <v>235</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -6270,7 +6288,7 @@
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B37" s="7">
         <v>46430</v>
@@ -6280,7 +6298,7 @@
         <v>Friday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>37</v>
@@ -6292,16 +6310,16 @@
         <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J37" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M37" t="s">
         <v>37</v>
@@ -6313,10 +6331,10 @@
         <v>30</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -6331,7 +6349,7 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B38" s="7">
         <v>46441</v>
@@ -6344,7 +6362,7 @@
         <v>36</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>38</v>
@@ -6353,22 +6371,22 @@
         <v>80</v>
       </c>
       <c r="H38" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I38" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J38" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N38" t="s">
         <v>29</v>
@@ -6377,13 +6395,13 @@
         <v>30</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q38" s="9" t="s">
-        <v>309</v>
+        <v>222</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>310</v>
       </c>
       <c r="R38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S38" t="s">
         <v>33</v>
@@ -6396,9 +6414,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
-        <v>310</v>
+    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>311</v>
       </c>
       <c r="B39" s="7">
         <v>46441</v>
@@ -6408,34 +6426,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G39" s="2">
         <v>80</v>
       </c>
       <c r="H39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J39" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M39" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N39" t="s">
         <v>29</v>
@@ -6444,28 +6462,28 @@
         <v>29</v>
       </c>
       <c r="P39" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q39" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R39" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="S39" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T39" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U39" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B40" s="7">
         <v>46444</v>
@@ -6475,7 +6493,7 @@
         <v>Friday</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>23</v>
@@ -6487,19 +6505,19 @@
         <v>100</v>
       </c>
       <c r="H40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -6510,11 +6528,11 @@
       <c r="O40" t="s">
         <v>30</v>
       </c>
-      <c r="Q40" s="9" t="s">
-        <v>315</v>
+      <c r="Q40" s="8" t="s">
+        <v>316</v>
       </c>
       <c r="R40" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S40" t="s">
         <v>33</v>
@@ -6556,9 +6574,9 @@
     <hyperlink ref="Q39" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6649,8 +6667,8 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>317</v>
+      <c r="A2" s="9" t="s">
+        <v>318</v>
       </c>
       <c r="B2" s="7">
         <v>46447</v>
@@ -6663,31 +6681,31 @@
         <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G2" s="2">
         <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -6696,19 +6714,19 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R2" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="S2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U2" t="b">
         <f>FALSE()</f>
@@ -6717,7 +6735,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B3" s="7">
         <v>46448</v>
@@ -6727,28 +6745,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2">
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M3" t="s">
         <v>52</v>
@@ -6759,11 +6777,11 @@
       <c r="O3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="9" t="s">
-        <v>328</v>
+      <c r="Q3" s="8" t="s">
+        <v>329</v>
       </c>
       <c r="R3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -6778,7 +6796,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B4" s="7">
         <v>46449</v>
@@ -6788,10 +6806,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>38</v>
@@ -6800,19 +6818,19 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -6821,13 +6839,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>333</v>
+        <v>261</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="R4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -6842,7 +6860,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B5" s="7">
         <v>46450</v>
@@ -6864,19 +6882,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M5" t="s">
         <v>37</v>
@@ -6888,13 +6906,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>338</v>
+        <v>161</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="R5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -6909,7 +6927,7 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B6" s="7">
         <v>46455</v>
@@ -6919,10 +6937,10 @@
         <v>Tuesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>38</v>
@@ -6931,19 +6949,19 @@
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s">
         <v>29</v>
@@ -6952,13 +6970,13 @@
         <v>30</v>
       </c>
       <c r="P6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -6972,8 +6990,8 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>343</v>
+      <c r="A7" s="9" t="s">
+        <v>344</v>
       </c>
       <c r="B7" s="7">
         <v>46455</v>
@@ -6983,34 +7001,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G7" s="2">
         <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -7019,19 +7037,19 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="S7" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T7" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U7" t="b">
         <f>FALSE()</f>
@@ -7040,7 +7058,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B8" s="7">
         <v>46456</v>
@@ -7050,10 +7068,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -7062,19 +7080,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -7083,10 +7101,10 @@
         <v>29</v>
       </c>
       <c r="P8" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q8" s="9" t="s">
         <v>235</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -7101,7 +7119,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B9" s="7">
         <v>46456</v>
@@ -7111,7 +7129,7 @@
         <v>Wednesday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>46</v>
@@ -7123,19 +7141,19 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M9" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -7144,13 +7162,13 @@
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>349</v>
+        <v>252</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>350</v>
       </c>
       <c r="R9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -7165,7 +7183,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B10" s="7">
         <v>46457</v>
@@ -7175,7 +7193,7 @@
         <v>Thursday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>37</v>
@@ -7187,16 +7205,16 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M10" t="s">
         <v>37</v>
@@ -7207,11 +7225,11 @@
       <c r="O10" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="9" t="s">
-        <v>352</v>
+      <c r="Q10" s="8" t="s">
+        <v>353</v>
       </c>
       <c r="R10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -7226,7 +7244,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B11" s="7">
         <v>46462</v>
@@ -7239,7 +7257,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
@@ -7248,22 +7266,22 @@
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -7271,11 +7289,11 @@
       <c r="O11" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="9" t="s">
-        <v>355</v>
+      <c r="Q11" s="8" t="s">
+        <v>356</v>
       </c>
       <c r="R11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -7290,7 +7308,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B12" s="7">
         <v>46462</v>
@@ -7300,7 +7318,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>46</v>
@@ -7312,19 +7330,19 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -7333,13 +7351,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>358</v>
+        <v>266</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>359</v>
       </c>
       <c r="R12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -7354,7 +7372,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B13" s="7">
         <v>46463</v>
@@ -7376,19 +7394,19 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M13" t="s">
         <v>52</v>
@@ -7402,11 +7420,11 @@
       <c r="P13" t="s">
         <v>55</v>
       </c>
-      <c r="Q13" s="9" t="s">
-        <v>362</v>
+      <c r="Q13" s="8" t="s">
+        <v>363</v>
       </c>
       <c r="R13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -7421,7 +7439,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B14" s="7">
         <v>46464</v>
@@ -7431,10 +7449,10 @@
         <v>Thursday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -7443,22 +7461,22 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -7466,11 +7484,11 @@
       <c r="O14" t="s">
         <v>30</v>
       </c>
-      <c r="Q14" s="9" t="s">
-        <v>367</v>
+      <c r="Q14" s="8" t="s">
+        <v>368</v>
       </c>
       <c r="R14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -7485,7 +7503,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B15" s="7">
         <v>46468</v>
@@ -7507,19 +7525,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M15" t="s">
         <v>37</v>
@@ -7530,11 +7548,11 @@
       <c r="O15" t="s">
         <v>30</v>
       </c>
-      <c r="Q15" s="9" t="s">
-        <v>370</v>
+      <c r="Q15" s="8" t="s">
+        <v>371</v>
       </c>
       <c r="R15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -7549,7 +7567,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B16" s="7">
         <v>46469</v>
@@ -7559,31 +7577,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -7592,13 +7610,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q16" s="9" t="s">
         <v>377</v>
       </c>
+      <c r="Q16" s="8" t="s">
+        <v>378</v>
+      </c>
       <c r="R16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -7613,7 +7631,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B17" s="7">
         <v>46470</v>
@@ -7635,19 +7653,19 @@
         <v>80</v>
       </c>
       <c r="H17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K17" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M17" t="s">
         <v>46</v>
@@ -7658,8 +7676,8 @@
       <c r="O17" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="9" t="s">
-        <v>381</v>
+      <c r="Q17" s="8" t="s">
+        <v>382</v>
       </c>
       <c r="R17" t="s">
         <v>49</v>
@@ -7677,7 +7695,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B18" s="7">
         <v>46486</v>
@@ -7687,10 +7705,10 @@
         <v>Friday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>38</v>
@@ -7699,22 +7717,22 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I18" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J18" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K18" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L18" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M18" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N18" t="s">
         <v>29</v>
@@ -7723,13 +7741,13 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>383</v>
+        <v>115</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>384</v>
       </c>
       <c r="R18" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -7744,7 +7762,7 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B19" s="7">
         <v>46492</v>
@@ -7754,7 +7772,7 @@
         <v>Thursday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>37</v>
@@ -7766,16 +7784,16 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
@@ -7787,13 +7805,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q19" s="9" t="s">
         <v>387</v>
       </c>
+      <c r="Q19" s="8" t="s">
+        <v>388</v>
+      </c>
       <c r="R19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -7808,7 +7826,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B20" s="7">
         <v>46496</v>
@@ -7818,7 +7836,7 @@
         <v>Monday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>23</v>
@@ -7830,19 +7848,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -7853,11 +7871,11 @@
       <c r="O20" t="s">
         <v>30</v>
       </c>
-      <c r="Q20" s="9" t="s">
-        <v>391</v>
+      <c r="Q20" s="8" t="s">
+        <v>392</v>
       </c>
       <c r="R20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -7872,7 +7890,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B21" s="7">
         <v>46500</v>
@@ -7882,31 +7900,31 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2">
         <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I21" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K21" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -7915,13 +7933,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R21" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -7936,7 +7954,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B22" s="7">
         <v>46505</v>
@@ -7946,28 +7964,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G22" s="2">
         <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J22" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M22" t="s">
         <v>52</v>
@@ -7978,11 +7996,11 @@
       <c r="O22" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" s="9" t="s">
-        <v>398</v>
+      <c r="Q22" s="8" t="s">
+        <v>399</v>
       </c>
       <c r="R22" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -7997,7 +8015,7 @@
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B23" s="7">
         <v>46506</v>
@@ -8007,7 +8025,7 @@
         <v>Thursday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>37</v>
@@ -8019,16 +8037,16 @@
         <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I23" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J23" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K23" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M23" t="s">
         <v>37</v>
@@ -8040,13 +8058,13 @@
         <v>29</v>
       </c>
       <c r="P23" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R23" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -8061,7 +8079,7 @@
     </row>
     <row r="24" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B24" s="7">
         <v>46507</v>
@@ -8071,7 +8089,7 @@
         <v>Friday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
@@ -8083,19 +8101,19 @@
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M24" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -8104,13 +8122,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>400</v>
+        <v>126</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>401</v>
       </c>
       <c r="R24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -8125,7 +8143,7 @@
     </row>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B25" s="7">
         <v>46512</v>
@@ -8135,10 +8153,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>38</v>
@@ -8147,22 +8165,22 @@
         <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I25" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J25" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L25" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -8170,11 +8188,11 @@
       <c r="O25" t="s">
         <v>30</v>
       </c>
-      <c r="Q25" s="9" t="s">
-        <v>403</v>
+      <c r="Q25" s="8" t="s">
+        <v>404</v>
       </c>
       <c r="R25" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -8189,7 +8207,7 @@
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B26" s="7">
         <v>46512</v>
@@ -8211,19 +8229,19 @@
         <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I26" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K26" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L26" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M26" t="s">
         <v>46</v>
@@ -8234,8 +8252,8 @@
       <c r="O26" t="s">
         <v>30</v>
       </c>
-      <c r="Q26" s="9" t="s">
-        <v>405</v>
+      <c r="Q26" s="8" t="s">
+        <v>406</v>
       </c>
       <c r="R26" t="s">
         <v>49</v>
@@ -8253,7 +8271,7 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B27" s="7">
         <v>46513</v>
@@ -8263,7 +8281,7 @@
         <v>Thursday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>37</v>
@@ -8275,16 +8293,16 @@
         <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I27" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K27" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M27" t="s">
         <v>37</v>
@@ -8295,11 +8313,11 @@
       <c r="O27" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="9" t="s">
-        <v>406</v>
+      <c r="Q27" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="R27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -8313,8 +8331,8 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>407</v>
+      <c r="A28" s="9" t="s">
+        <v>408</v>
       </c>
       <c r="B28" s="7">
         <v>46517</v>
@@ -8327,31 +8345,31 @@
         <v>36</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G28" s="2">
         <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I28" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J28" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K28" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L28" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M28" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
@@ -8360,19 +8378,19 @@
         <v>29</v>
       </c>
       <c r="P28" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R28" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="S28" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T28" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U28" t="b">
         <f>FALSE()</f>
@@ -8381,7 +8399,7 @@
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B29" s="7">
         <v>46518</v>
@@ -8394,7 +8412,7 @@
         <v>36</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>38</v>
@@ -8403,22 +8421,22 @@
         <v>80</v>
       </c>
       <c r="H29" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I29" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J29" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L29" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N29" t="s">
         <v>29</v>
@@ -8427,13 +8445,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>412</v>
+        <v>222</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>413</v>
       </c>
       <c r="R29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -8448,7 +8466,7 @@
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B30" s="7">
         <v>46519</v>
@@ -8458,10 +8476,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -8470,19 +8488,19 @@
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I30" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -8491,13 +8509,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q30" s="9" t="s">
-        <v>414</v>
+        <v>235</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>415</v>
       </c>
       <c r="R30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -8512,7 +8530,7 @@
     </row>
     <row r="31" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B31" s="7">
         <v>46520</v>
@@ -8522,10 +8540,10 @@
         <v>Thursday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>38</v>
@@ -8534,19 +8552,19 @@
         <v>80</v>
       </c>
       <c r="H31" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I31" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J31" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K31" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M31" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N31" t="s">
         <v>30</v>
@@ -8554,11 +8572,11 @@
       <c r="O31" t="s">
         <v>30</v>
       </c>
-      <c r="Q31" s="9" t="s">
-        <v>416</v>
+      <c r="Q31" s="8" t="s">
+        <v>417</v>
       </c>
       <c r="R31" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -8573,7 +8591,7 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B32" s="7">
         <v>46525</v>
@@ -8595,19 +8613,19 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I32" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K32" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L32" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M32" t="s">
         <v>52</v>
@@ -8621,11 +8639,11 @@
       <c r="P32" t="s">
         <v>55</v>
       </c>
-      <c r="Q32" s="9" t="s">
-        <v>419</v>
+      <c r="Q32" s="8" t="s">
+        <v>420</v>
       </c>
       <c r="R32" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -8640,7 +8658,7 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B33" s="7">
         <v>46526</v>
@@ -8650,31 +8668,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G33" s="2">
         <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I33" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J33" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K33" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -8683,13 +8701,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>421</v>
+        <v>152</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>422</v>
       </c>
       <c r="R33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -8704,7 +8722,7 @@
     </row>
     <row r="34" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B34" s="7">
         <v>46527</v>
@@ -8714,7 +8732,7 @@
         <v>Thursday</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>37</v>
@@ -8726,16 +8744,16 @@
         <v>80</v>
       </c>
       <c r="H34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K34" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M34" t="s">
         <v>37</v>
@@ -8747,13 +8765,13 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R34" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S34" t="s">
         <v>33</v>
@@ -8767,8 +8785,8 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>423</v>
+      <c r="A35" s="9" t="s">
+        <v>424</v>
       </c>
       <c r="B35" s="7">
         <v>46527</v>
@@ -8778,34 +8796,34 @@
         <v>Thursday</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G35" s="2">
         <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I35" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K35" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L35" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M35" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N35" t="s">
         <v>29</v>
@@ -8814,28 +8832,28 @@
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q35" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R35" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="S35" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T35" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U35" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B36" s="7">
         <v>46533</v>
@@ -8845,31 +8863,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G36" s="2">
         <v>12</v>
       </c>
       <c r="H36" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J36" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K36" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N36" t="s">
         <v>29</v>
@@ -8877,11 +8895,11 @@
       <c r="O36" t="s">
         <v>30</v>
       </c>
-      <c r="Q36" s="9" t="s">
-        <v>428</v>
+      <c r="Q36" s="8" t="s">
+        <v>429</v>
       </c>
       <c r="R36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -8894,9 +8912,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B37" s="7">
         <v>46534</v>
@@ -8906,10 +8924,10 @@
         <v>Thursday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>38</v>
@@ -8918,19 +8936,19 @@
         <v>80</v>
       </c>
       <c r="H37" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I37" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J37" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K37" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M37" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N37" t="s">
         <v>30</v>
@@ -8939,7 +8957,7 @@
         <v>29</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -9068,8 +9086,8 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>430</v>
+      <c r="A2" s="9" t="s">
+        <v>431</v>
       </c>
       <c r="B2" s="7">
         <v>46546</v>
@@ -9079,34 +9097,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G2" s="2">
         <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -9115,19 +9133,19 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R2" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="S2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U2" t="b">
         <f>FALSE()</f>
@@ -9136,7 +9154,7 @@
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B3" s="7">
         <v>46547</v>
@@ -9146,10 +9164,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>38</v>
@@ -9158,22 +9176,22 @@
         <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N3" t="s">
         <v>29</v>
@@ -9182,13 +9200,13 @@
         <v>30</v>
       </c>
       <c r="P3" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>441</v>
+        <v>115</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="R3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -9203,7 +9221,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B4" s="7">
         <v>46548</v>
@@ -9225,19 +9243,19 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M4" t="s">
         <v>37</v>
@@ -9249,13 +9267,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>446</v>
+        <v>161</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>447</v>
       </c>
       <c r="R4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -9270,7 +9288,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B5" s="7">
         <v>46552</v>
@@ -9280,7 +9298,7 @@
         <v>Monday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
@@ -9292,19 +9310,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
@@ -9313,13 +9331,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>449</v>
+        <v>230</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="R5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -9334,7 +9352,7 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B6" s="7">
         <v>46553</v>
@@ -9344,7 +9362,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
@@ -9356,19 +9374,19 @@
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -9379,11 +9397,11 @@
       <c r="O6" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="9" t="s">
-        <v>453</v>
+      <c r="Q6" s="8" t="s">
+        <v>454</v>
       </c>
       <c r="R6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -9398,7 +9416,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B7" s="7">
         <v>46554</v>
@@ -9408,10 +9426,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>38</v>
@@ -9420,19 +9438,19 @@
         <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N7" t="s">
         <v>30</v>
@@ -9441,10 +9459,10 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>414</v>
+        <v>235</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>415</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -9459,7 +9477,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B8" s="7">
         <v>46561</v>
@@ -9469,10 +9487,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -9481,19 +9499,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -9502,13 +9520,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>456</v>
+        <v>266</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="R8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -9523,7 +9541,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B9" s="7">
         <v>46562</v>
@@ -9536,7 +9554,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>38</v>
@@ -9545,22 +9563,22 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -9569,10 +9587,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -9587,7 +9605,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B10" s="7">
         <v>46568</v>
@@ -9609,19 +9627,19 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M10" t="s">
         <v>46</v>
@@ -9632,8 +9650,8 @@
       <c r="O10" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="9" t="s">
-        <v>463</v>
+      <c r="Q10" s="8" t="s">
+        <v>464</v>
       </c>
       <c r="R10" t="s">
         <v>49</v>
@@ -9651,7 +9669,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B11" s="7">
         <v>46569</v>
@@ -9661,10 +9679,10 @@
         <v>Thursday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
@@ -9673,22 +9691,22 @@
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -9696,11 +9714,11 @@
       <c r="O11" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="9" t="s">
-        <v>466</v>
+      <c r="Q11" s="8" t="s">
+        <v>467</v>
       </c>
       <c r="R11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -9715,7 +9733,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B12" s="7">
         <v>46570</v>
@@ -9725,31 +9743,31 @@
         <v>Friday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I12" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -9758,13 +9776,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>469</v>
+        <v>126</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="R12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -9778,8 +9796,8 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>471</v>
+      <c r="A13" s="9" t="s">
+        <v>472</v>
       </c>
       <c r="B13" s="7">
         <v>46574</v>
@@ -9792,31 +9810,31 @@
         <v>51</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G13" s="2">
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L13" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M13" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -9825,19 +9843,19 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R13" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="S13" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U13" t="b">
         <f>FALSE()</f>
@@ -9846,7 +9864,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B14" s="7">
         <v>46575</v>
@@ -9856,10 +9874,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -9868,19 +9886,19 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N14" t="s">
         <v>30</v>
@@ -9889,10 +9907,10 @@
         <v>29</v>
       </c>
       <c r="P14" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>456</v>
+        <v>266</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -9907,7 +9925,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B15" s="7">
         <v>46575</v>
@@ -9917,10 +9935,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -9929,19 +9947,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -9950,10 +9968,10 @@
         <v>29</v>
       </c>
       <c r="P15" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>414</v>
+        <v>235</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>415</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -9968,7 +9986,7 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B16" s="7">
         <v>46576</v>
@@ -9978,7 +9996,7 @@
         <v>Thursday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>46</v>
@@ -9990,19 +10008,19 @@
         <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I16" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J16" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K16" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M16" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -10011,13 +10029,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>476</v>
+        <v>126</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="R16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -10031,8 +10049,8 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>477</v>
+      <c r="A17" s="9" t="s">
+        <v>478</v>
       </c>
       <c r="B17" s="7">
         <v>46582</v>
@@ -10042,34 +10060,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G17" s="2">
         <v>80</v>
       </c>
       <c r="H17" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L17" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M17" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -10078,19 +10096,19 @@
         <v>29</v>
       </c>
       <c r="P17" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="S17" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T17" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U17" t="b">
         <f>FALSE()</f>
@@ -10099,7 +10117,7 @@
     </row>
     <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B18" s="7">
         <v>46589</v>
@@ -10109,10 +10127,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>38</v>
@@ -10121,19 +10139,19 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J18" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K18" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M18" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
@@ -10142,10 +10160,10 @@
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>456</v>
+        <v>266</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -10159,8 +10177,8 @@
       </c>
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>481</v>
+      <c r="A19" s="9" t="s">
+        <v>482</v>
       </c>
       <c r="B19" s="7">
         <v>46604</v>
@@ -10170,34 +10188,34 @@
         <v>Thursday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G19" s="2">
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I19" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M19" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
@@ -10206,28 +10224,28 @@
         <v>29</v>
       </c>
       <c r="P19" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R19" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="S19" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T19" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="U19" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B20" s="7">
         <v>46612</v>
@@ -10237,10 +10255,10 @@
         <v>Friday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>38</v>
@@ -10249,22 +10267,22 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I20" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J20" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K20" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L20" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
@@ -10273,13 +10291,13 @@
         <v>30</v>
       </c>
       <c r="P20" t="s">
-        <v>485</v>
-      </c>
-      <c r="Q20" s="9" t="s">
         <v>486</v>
       </c>
+      <c r="Q20" s="8" t="s">
+        <v>487</v>
+      </c>
       <c r="R20" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1BBA80-B57F-4B87-B588-795BFB7B42CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92B8CDA-386D-4217-BF1E-E6EC7576620B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="490">
   <si>
     <t>Event Name</t>
   </si>
@@ -1601,7 +1601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1627,6 +1627,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2617,8 +2618,8 @@
       <c r="F10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="2">
-        <v>80</v>
+      <c r="G10" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H10" t="s">
         <v>25</v>
@@ -2812,8 +2813,8 @@
       <c r="F13" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="2">
-        <v>80</v>
+      <c r="G13" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H13" t="s">
         <v>25</v>
@@ -3132,14 +3133,14 @@
       <c r="D18" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="2">
-        <v>80</v>
+      <c r="G18" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H18" t="s">
         <v>25</v>
@@ -4645,14 +4646,14 @@
       <c r="D11" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G11" s="2">
-        <v>80</v>
+      <c r="G11" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H11" t="s">
         <v>176</v>
@@ -6111,14 +6112,14 @@
       <c r="D34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="G34" s="2">
-        <v>80</v>
+      <c r="G34" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H34" t="s">
         <v>176</v>
@@ -6428,14 +6429,14 @@
       <c r="D39" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="G39" s="2">
-        <v>80</v>
+      <c r="G39" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H39" t="s">
         <v>176</v>
@@ -6680,14 +6681,14 @@
       <c r="D2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="G2" s="2">
-        <v>80</v>
+      <c r="G2" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H2" t="s">
         <v>320</v>
@@ -7003,14 +7004,14 @@
       <c r="D7" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="2">
-        <v>80</v>
+      <c r="G7" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H7" t="s">
         <v>320</v>
@@ -8344,14 +8345,14 @@
       <c r="D28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="G28" s="2">
-        <v>80</v>
+      <c r="G28" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H28" t="s">
         <v>320</v>
@@ -8798,14 +8799,14 @@
       <c r="D35" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="G35" s="2">
-        <v>80</v>
+      <c r="G35" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H35" t="s">
         <v>320</v>
@@ -9099,14 +9100,14 @@
       <c r="D2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="G2" s="2">
-        <v>80</v>
+      <c r="G2" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H2" t="s">
         <v>433</v>
@@ -9809,14 +9810,14 @@
       <c r="D13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="G13" s="2">
-        <v>80</v>
+      <c r="G13" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H13" t="s">
         <v>433</v>
@@ -10062,14 +10063,14 @@
       <c r="D17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G17" s="2">
-        <v>80</v>
+      <c r="G17" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H17" t="s">
         <v>433</v>
@@ -10190,14 +10191,14 @@
       <c r="D19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="G19" s="2">
-        <v>80</v>
+      <c r="G19" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H19" t="s">
         <v>433</v>

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92B8CDA-386D-4217-BF1E-E6EC7576620B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49436EFB-FAF2-4A20-B761-600C6DE6C242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="490">
   <si>
     <t>Event Name</t>
   </si>
@@ -4201,14 +4201,14 @@
       <c r="D4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G4" s="2">
-        <v>80</v>
+      <c r="G4" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="H4" t="s">
         <v>176</v>

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49436EFB-FAF2-4A20-B761-600C6DE6C242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E41DC1-5AFE-47EB-AC54-7C5FD3311ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -305,18 +305,12 @@
     <t>External</t>
   </si>
   <si>
-    <t>How Can a Playful Pedagogy Work Within a Home-Based Childcare Setting? With Michelle Malamo</t>
-  </si>
-  <si>
     <t>PD PSED RP1-26-27</t>
   </si>
   <si>
     <t>Presenter: Michelle Malamo. Can record.</t>
   </si>
   <si>
-    <t>https://beyth.co.uk/course/how-can-a-playful-pedagogy-work-within-a-home-based-childcare-setting-with-michelle-malamo/</t>
-  </si>
-  <si>
     <t>A webinar for childminders exploring playful, therapeutic practices that meet the needs of babies and young children through play, considering how different types of play, flexible play environments and intentional adult responses support children's development, wellbeing and learning. Participants will reflect on embedding playful pedagogy within home-based childcare settings and leave with practical strategies to implement immediately.</t>
   </si>
   <si>
@@ -1509,6 +1503,12 @@
   </si>
   <si>
     <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-october-2026/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/how-can-a-playful-pedagogy-work-within-a-home-based-childcare-setting-michelle-malomo/</t>
+  </si>
+  <si>
+    <t>How Can a Playful Pedagogy Work Within a Home-Based Childcare Setting? With Michelle Malomo</t>
   </si>
 </sst>
 </file>
@@ -1518,7 +1518,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1541,6 +1541,14 @@
       <sz val="12"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1598,10 +1606,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1628,8 +1637,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2649,7 +2660,7 @@
         <v>84</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="R10" t="s">
         <v>86</v>
@@ -2667,7 +2678,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>88</v>
+        <v>489</v>
       </c>
       <c r="B11" s="7">
         <v>46315</v>
@@ -2698,7 +2709,7 @@
         <v>64</v>
       </c>
       <c r="K11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M11" t="s">
         <v>23</v>
@@ -2710,13 +2721,13 @@
         <v>30</v>
       </c>
       <c r="P11" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="R11" t="s">
         <v>90</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="R11" t="s">
-        <v>92</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -2731,7 +2742,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B12" s="7">
         <v>46315</v>
@@ -2741,13 +2752,13 @@
         <v>Tuesday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
@@ -2765,22 +2776,22 @@
         <v>28</v>
       </c>
       <c r="M12" t="s">
+        <v>94</v>
+      </c>
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q12" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="N12" t="s">
-        <v>30</v>
-      </c>
-      <c r="O12" t="s">
-        <v>30</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
         <v>97</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="R12" t="s">
-        <v>99</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -2795,7 +2806,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B13" s="7">
         <v>46316</v>
@@ -2805,13 +2816,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G13" s="15" t="s">
         <v>87</v>
@@ -2829,7 +2840,7 @@
         <v>28</v>
       </c>
       <c r="L13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M13" t="s">
         <v>75</v>
@@ -2841,13 +2852,13 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="R13" t="s">
         <v>104</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="R13" t="s">
-        <v>106</v>
       </c>
       <c r="S13" t="s">
         <v>80</v>
@@ -2862,7 +2873,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B14" s="7">
         <v>46316</v>
@@ -2875,7 +2886,7 @@
         <v>79</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -2893,25 +2904,25 @@
         <v>64</v>
       </c>
       <c r="K14" t="s">
+        <v>107</v>
+      </c>
+      <c r="M14" t="s">
+        <v>106</v>
+      </c>
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="M14" t="s">
-        <v>108</v>
-      </c>
-      <c r="N14" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
         <v>110</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="R14" t="s">
-        <v>112</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -2926,7 +2937,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B15" s="7">
         <v>46317</v>
@@ -2936,7 +2947,7 @@
         <v>Thursday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>83</v>
@@ -2957,7 +2968,7 @@
         <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L15" t="s">
         <v>82</v>
@@ -2972,13 +2983,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R15" t="s">
         <v>115</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="R15" t="s">
-        <v>117</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -2993,7 +3004,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B16" s="7">
         <v>46317</v>
@@ -3003,10 +3014,10 @@
         <v>Thursday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>38</v>
@@ -3024,25 +3035,25 @@
         <v>64</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N16" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="N16" t="s">
-        <v>29</v>
-      </c>
-      <c r="O16" t="s">
-        <v>30</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="R16" t="s">
         <v>121</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="R16" t="s">
-        <v>123</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -3057,7 +3068,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B17" s="7">
         <v>46318</v>
@@ -3067,7 +3078,7 @@
         <v>Friday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>46</v>
@@ -3091,7 +3102,7 @@
         <v>28</v>
       </c>
       <c r="M17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -3100,13 +3111,13 @@
         <v>30</v>
       </c>
       <c r="P17" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="R17" t="s">
         <v>126</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="R17" t="s">
-        <v>128</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -3121,7 +3132,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B18" s="7">
         <v>46328</v>
@@ -3131,13 +3142,13 @@
         <v>Monday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G18" s="15" t="s">
         <v>87</v>
@@ -3155,7 +3166,7 @@
         <v>28</v>
       </c>
       <c r="L18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M18" t="s">
         <v>75</v>
@@ -3167,13 +3178,13 @@
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q18" s="8" t="s">
         <v>85</v>
       </c>
       <c r="R18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S18" t="s">
         <v>80</v>
@@ -3188,7 +3199,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B19" s="7">
         <v>46330</v>
@@ -3219,7 +3230,7 @@
         <v>64</v>
       </c>
       <c r="K19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M19" t="s">
         <v>83</v>
@@ -3231,10 +3242,10 @@
         <v>30</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="R19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -3249,7 +3260,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B20" s="7">
         <v>46331</v>
@@ -3292,10 +3303,10 @@
         <v>30</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -3310,7 +3321,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B21" s="7">
         <v>46332</v>
@@ -3320,10 +3331,10 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>81</v>
@@ -3341,10 +3352,10 @@
         <v>27</v>
       </c>
       <c r="K21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -3353,13 +3364,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="R21" t="s">
         <v>141</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="R21" t="s">
-        <v>143</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -3374,7 +3385,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B22" s="7">
         <v>46335</v>
@@ -3387,7 +3398,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>38</v>
@@ -3405,25 +3416,25 @@
         <v>39</v>
       </c>
       <c r="K22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L22" t="s">
+        <v>144</v>
+      </c>
+      <c r="M22" t="s">
+        <v>143</v>
+      </c>
+      <c r="N22" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="R22" t="s">
         <v>146</v>
-      </c>
-      <c r="M22" t="s">
-        <v>145</v>
-      </c>
-      <c r="N22" t="s">
-        <v>29</v>
-      </c>
-      <c r="O22" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="R22" t="s">
-        <v>148</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -3438,7 +3449,7 @@
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B23" s="7">
         <v>46336</v>
@@ -3448,13 +3459,13 @@
         <v>Tuesday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2">
         <v>16</v>
@@ -3472,22 +3483,22 @@
         <v>28</v>
       </c>
       <c r="M23" t="s">
+        <v>94</v>
+      </c>
+      <c r="N23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O23" t="s">
+        <v>29</v>
+      </c>
+      <c r="P23" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q23" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="N23" t="s">
-        <v>30</v>
-      </c>
-      <c r="O23" t="s">
-        <v>29</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="R23" t="s">
         <v>97</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="R23" t="s">
-        <v>99</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -3502,7 +3513,7 @@
     </row>
     <row r="24" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B24" s="7">
         <v>46337</v>
@@ -3512,13 +3523,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2">
         <v>16</v>
@@ -3536,7 +3547,7 @@
         <v>28</v>
       </c>
       <c r="M24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -3545,13 +3556,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="R24" t="s">
         <v>152</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="R24" t="s">
-        <v>154</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -3566,7 +3577,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B25" s="7">
         <v>46338</v>
@@ -3576,7 +3587,7 @@
         <v>Thursday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>80</v>
@@ -3597,7 +3608,7 @@
         <v>28</v>
       </c>
       <c r="L25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -3606,10 +3617,10 @@
         <v>30</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S25" t="s">
         <v>80</v>
@@ -3624,7 +3635,7 @@
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B26" s="7">
         <v>46344</v>
@@ -3655,7 +3666,7 @@
         <v>64</v>
       </c>
       <c r="K26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M26" t="s">
         <v>83</v>
@@ -3667,7 +3678,7 @@
         <v>29</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -3682,7 +3693,7 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B27" s="7">
         <v>46345</v>
@@ -3728,13 +3739,13 @@
         <v>30</v>
       </c>
       <c r="P27" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="R27" t="s">
         <v>161</v>
-      </c>
-      <c r="Q27" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="R27" t="s">
-        <v>163</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -3749,7 +3760,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B28" s="7">
         <v>46351</v>
@@ -3762,7 +3773,7 @@
         <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -3780,10 +3791,10 @@
         <v>64</v>
       </c>
       <c r="K28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
@@ -3792,13 +3803,13 @@
         <v>30</v>
       </c>
       <c r="P28" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="R28" t="s">
         <v>165</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="R28" t="s">
-        <v>167</v>
       </c>
       <c r="S28" t="s">
         <v>33</v>
@@ -3813,7 +3824,7 @@
     </row>
     <row r="29" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B29" s="7">
         <v>46352</v>
@@ -3844,7 +3855,7 @@
         <v>64</v>
       </c>
       <c r="K29" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M29" t="s">
         <v>37</v>
@@ -3856,10 +3867,10 @@
         <v>30</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R29" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -3874,7 +3885,7 @@
     </row>
     <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B30" s="7">
         <v>46352</v>
@@ -3923,10 +3934,10 @@
         <v>55</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R30" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -3965,11 +3976,12 @@
     <hyperlink ref="Q25" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="Q26" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="Q28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="Q11" r:id="rId15" xr:uid="{0C4392EE-38FB-4C24-9A4D-9185E1338FE4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4061,7 +4073,7 @@
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B2" s="7">
         <v>46357</v>
@@ -4083,19 +4095,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J2" t="s">
         <v>176</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>177</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>178</v>
-      </c>
-      <c r="K2" t="s">
-        <v>179</v>
-      </c>
-      <c r="L2" t="s">
-        <v>180</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
@@ -4107,10 +4119,10 @@
         <v>30</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S2" t="s">
         <v>33</v>
@@ -4125,7 +4137,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B3" s="7">
         <v>46357</v>
@@ -4135,46 +4147,46 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2">
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K3" t="s">
         <v>177</v>
       </c>
-      <c r="J3" t="s">
-        <v>184</v>
-      </c>
-      <c r="K3" t="s">
-        <v>179</v>
-      </c>
       <c r="M3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>97</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="R3" t="s">
-        <v>99</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -4189,7 +4201,7 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B4" s="7">
         <v>46357</v>
@@ -4199,31 +4211,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J4" t="s">
         <v>176</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>177</v>
       </c>
-      <c r="J4" t="s">
-        <v>178</v>
-      </c>
-      <c r="K4" t="s">
-        <v>179</v>
-      </c>
       <c r="L4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M4" t="s">
         <v>75</v>
@@ -4235,13 +4247,13 @@
         <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Q4" s="8" t="s">
         <v>85</v>
       </c>
       <c r="R4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S4" t="s">
         <v>80</v>
@@ -4256,7 +4268,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B5" s="7">
         <v>46358</v>
@@ -4278,19 +4290,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J5" t="s">
         <v>176</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>177</v>
       </c>
-      <c r="J5" t="s">
-        <v>178</v>
-      </c>
-      <c r="K5" t="s">
-        <v>179</v>
-      </c>
       <c r="L5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M5" t="s">
         <v>46</v>
@@ -4302,7 +4314,7 @@
         <v>30</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R5" t="s">
         <v>49</v>
@@ -4320,7 +4332,7 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B6" s="7">
         <v>46358</v>
@@ -4342,16 +4354,16 @@
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M6" t="s">
         <v>83</v>
@@ -4363,7 +4375,7 @@
         <v>29</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -4378,7 +4390,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B7" s="7">
         <v>46358</v>
@@ -4388,31 +4400,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G7" s="2">
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -4421,10 +4433,10 @@
         <v>30</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="R7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -4439,7 +4451,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B8" s="7">
         <v>46360</v>
@@ -4449,10 +4461,10 @@
         <v>Friday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -4461,19 +4473,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
+        <v>174</v>
+      </c>
+      <c r="I8" t="s">
+        <v>175</v>
+      </c>
+      <c r="J8" t="s">
         <v>176</v>
       </c>
-      <c r="I8" t="s">
-        <v>177</v>
-      </c>
-      <c r="J8" t="s">
-        <v>178</v>
-      </c>
       <c r="K8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M8" t="s">
         <v>75</v>
@@ -4485,13 +4497,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -4506,7 +4518,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B9" s="7">
         <v>46363</v>
@@ -4528,19 +4540,19 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I9" t="s">
+        <v>175</v>
+      </c>
+      <c r="J9" t="s">
         <v>176</v>
       </c>
-      <c r="I9" t="s">
-        <v>177</v>
-      </c>
-      <c r="J9" t="s">
-        <v>178</v>
-      </c>
       <c r="K9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M9" t="s">
         <v>37</v>
@@ -4552,10 +4564,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -4570,7 +4582,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B10" s="7">
         <v>46364</v>
@@ -4583,7 +4595,7 @@
         <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>38</v>
@@ -4592,34 +4604,34 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K10" t="s">
+        <v>208</v>
+      </c>
+      <c r="M10" t="s">
+        <v>207</v>
+      </c>
+      <c r="N10" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q10" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="M10" t="s">
-        <v>209</v>
-      </c>
-      <c r="N10" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="R10" t="s">
         <v>211</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="R10" t="s">
-        <v>213</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -4634,7 +4646,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="7">
         <v>46365</v>
@@ -4644,31 +4656,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G11" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" t="s">
         <v>176</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>177</v>
       </c>
-      <c r="J11" t="s">
-        <v>178</v>
-      </c>
-      <c r="K11" t="s">
-        <v>179</v>
-      </c>
       <c r="L11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M11" t="s">
         <v>83</v>
@@ -4680,7 +4692,7 @@
         <v>29</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="Q11" s="8" t="s">
         <v>85</v>
@@ -4701,7 +4713,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B12" s="7">
         <v>46366</v>
@@ -4714,7 +4726,7 @@
         <v>36</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>38</v>
@@ -4723,37 +4735,37 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
+        <v>174</v>
+      </c>
+      <c r="I12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J12" t="s">
         <v>176</v>
       </c>
-      <c r="I12" t="s">
-        <v>177</v>
-      </c>
-      <c r="J12" t="s">
-        <v>178</v>
-      </c>
       <c r="K12" t="s">
+        <v>218</v>
+      </c>
+      <c r="L12" t="s">
+        <v>219</v>
+      </c>
+      <c r="M12" t="s">
+        <v>106</v>
+      </c>
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" t="s">
         <v>220</v>
       </c>
-      <c r="L12" t="s">
+      <c r="Q12" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="M12" t="s">
-        <v>108</v>
-      </c>
-      <c r="N12" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" t="s">
-        <v>30</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
         <v>222</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="R12" t="s">
-        <v>224</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -4768,7 +4780,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B13" s="7">
         <v>46394</v>
@@ -4790,19 +4802,19 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I13" t="s">
+        <v>175</v>
+      </c>
+      <c r="J13" t="s">
+        <v>190</v>
+      </c>
+      <c r="K13" t="s">
         <v>177</v>
       </c>
-      <c r="J13" t="s">
-        <v>192</v>
-      </c>
-      <c r="K13" t="s">
-        <v>179</v>
-      </c>
       <c r="M13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -4811,13 +4823,13 @@
         <v>30</v>
       </c>
       <c r="P13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="R13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -4832,7 +4844,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B14" s="7">
         <v>46398</v>
@@ -4842,10 +4854,10 @@
         <v>Monday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -4854,34 +4866,34 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M14" t="s">
+        <v>227</v>
+      </c>
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q14" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="N14" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
         <v>230</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="R14" t="s">
-        <v>232</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -4896,7 +4908,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B15" s="7">
         <v>46400</v>
@@ -4906,10 +4918,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -4918,19 +4930,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -4939,13 +4951,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="R15" t="s">
         <v>235</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="R15" t="s">
-        <v>237</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -4960,7 +4972,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B16" s="7">
         <v>46402</v>
@@ -4970,31 +4982,31 @@
         <v>Friday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I16" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -5003,13 +5015,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="R16" t="s">
         <v>240</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="R16" t="s">
-        <v>242</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -5024,7 +5036,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B17" s="7">
         <v>46405</v>
@@ -5034,28 +5046,28 @@
         <v>Monday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G17" s="2">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K17" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M17" t="s">
         <v>52</v>
@@ -5067,10 +5079,10 @@
         <v>30</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="R17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -5085,7 +5097,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B18" s="7">
         <v>46407</v>
@@ -5095,28 +5107,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G18" s="2">
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K18" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M18" t="s">
         <v>52</v>
@@ -5128,10 +5140,10 @@
         <v>30</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -5146,7 +5158,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B19" s="7">
         <v>46407</v>
@@ -5168,19 +5180,19 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I19" t="s">
+        <v>175</v>
+      </c>
+      <c r="J19" t="s">
+        <v>190</v>
+      </c>
+      <c r="K19" t="s">
         <v>177</v>
       </c>
-      <c r="J19" t="s">
-        <v>192</v>
-      </c>
-      <c r="K19" t="s">
-        <v>179</v>
-      </c>
       <c r="M19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
@@ -5189,13 +5201,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="R19" t="s">
         <v>252</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="R19" t="s">
-        <v>254</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -5210,7 +5222,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B20" s="7">
         <v>46408</v>
@@ -5223,7 +5235,7 @@
         <v>36</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>38</v>
@@ -5232,34 +5244,34 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
+        <v>174</v>
+      </c>
+      <c r="I20" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" t="s">
         <v>176</v>
       </c>
-      <c r="I20" t="s">
-        <v>177</v>
-      </c>
-      <c r="J20" t="s">
-        <v>178</v>
-      </c>
       <c r="K20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s">
+        <v>254</v>
+      </c>
+      <c r="M20" t="s">
+        <v>143</v>
+      </c>
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="R20" t="s">
         <v>256</v>
-      </c>
-      <c r="M20" t="s">
-        <v>145</v>
-      </c>
-      <c r="N20" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="R20" t="s">
-        <v>258</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -5274,7 +5286,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B21" s="7">
         <v>46408</v>
@@ -5284,10 +5296,10 @@
         <v>Thursday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>38</v>
@@ -5296,34 +5308,34 @@
         <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M21" t="s">
+        <v>258</v>
+      </c>
+      <c r="N21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q21" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="N21" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" t="s">
-        <v>30</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="R21" t="s">
         <v>261</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="R21" t="s">
-        <v>263</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -5338,7 +5350,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B22" s="7">
         <v>46414</v>
@@ -5360,34 +5372,34 @@
         <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M22" t="s">
+        <v>263</v>
+      </c>
+      <c r="N22" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q22" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="N22" t="s">
-        <v>30</v>
-      </c>
-      <c r="O22" t="s">
-        <v>30</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="R22" t="s">
         <v>266</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="R22" t="s">
-        <v>268</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -5402,7 +5414,7 @@
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B23" s="7">
         <v>46416</v>
@@ -5412,7 +5424,7 @@
         <v>Friday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>37</v>
@@ -5424,16 +5436,16 @@
         <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J23" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K23" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s">
         <v>37</v>
@@ -5445,10 +5457,10 @@
         <v>30</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -5463,7 +5475,7 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B24" s="7">
         <v>46420</v>
@@ -5473,7 +5485,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>83</v>
@@ -5485,19 +5497,19 @@
         <v>80</v>
       </c>
       <c r="H24" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" t="s">
         <v>176</v>
       </c>
-      <c r="I24" t="s">
-        <v>177</v>
-      </c>
-      <c r="J24" t="s">
-        <v>178</v>
-      </c>
       <c r="K24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s">
         <v>83</v>
@@ -5509,13 +5521,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -5530,7 +5542,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B25" s="7">
         <v>46420</v>
@@ -5540,28 +5552,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G25" s="2">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s">
         <v>52</v>
@@ -5573,13 +5585,13 @@
         <v>30</v>
       </c>
       <c r="P25" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="R25" t="s">
         <v>278</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="R25" t="s">
-        <v>280</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -5594,7 +5606,7 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B26" s="7">
         <v>46420</v>
@@ -5616,16 +5628,16 @@
         <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I26" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" t="s">
+        <v>190</v>
+      </c>
+      <c r="K26" t="s">
         <v>177</v>
-      </c>
-      <c r="J26" t="s">
-        <v>192</v>
-      </c>
-      <c r="K26" t="s">
-        <v>179</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -5637,13 +5649,13 @@
         <v>30</v>
       </c>
       <c r="P26" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="R26" t="s">
         <v>282</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="R26" t="s">
-        <v>284</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -5658,7 +5670,7 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B27" s="7">
         <v>46421</v>
@@ -5668,31 +5680,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G27" s="2">
         <v>12</v>
       </c>
       <c r="H27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K27" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N27" t="s">
         <v>29</v>
@@ -5701,10 +5713,10 @@
         <v>30</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="R27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -5719,7 +5731,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B28" s="7">
         <v>46421</v>
@@ -5741,19 +5753,19 @@
         <v>80</v>
       </c>
       <c r="H28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I28" t="s">
+        <v>175</v>
+      </c>
+      <c r="J28" t="s">
         <v>176</v>
       </c>
-      <c r="I28" t="s">
+      <c r="K28" t="s">
         <v>177</v>
       </c>
-      <c r="J28" t="s">
-        <v>178</v>
-      </c>
-      <c r="K28" t="s">
-        <v>179</v>
-      </c>
       <c r="L28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M28" t="s">
         <v>46</v>
@@ -5765,7 +5777,7 @@
         <v>30</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="R28" t="s">
         <v>49</v>
@@ -5783,7 +5795,7 @@
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B29" s="7">
         <v>46422</v>
@@ -5793,28 +5805,28 @@
         <v>Thursday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G29" s="2">
         <v>6</v>
       </c>
       <c r="H29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I29" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J29" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s">
         <v>52</v>
@@ -5826,13 +5838,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="R29" t="s">
         <v>278</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="R29" t="s">
-        <v>280</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -5847,7 +5859,7 @@
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B30" s="7">
         <v>46422</v>
@@ -5857,10 +5869,10 @@
         <v>Thursday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -5869,19 +5881,19 @@
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I30" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M30" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s">
         <v>29</v>
@@ -5890,13 +5902,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="R30" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -5911,7 +5923,7 @@
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B31" s="7">
         <v>46423</v>
@@ -5921,7 +5933,7 @@
         <v>Friday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>37</v>
@@ -5933,16 +5945,16 @@
         <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J31" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K31" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M31" t="s">
         <v>37</v>
@@ -5954,10 +5966,10 @@
         <v>30</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="R31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -5972,7 +5984,7 @@
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B32" s="7">
         <v>46426</v>
@@ -5994,19 +6006,19 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
+        <v>174</v>
+      </c>
+      <c r="I32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" t="s">
         <v>176</v>
       </c>
-      <c r="I32" t="s">
-        <v>177</v>
-      </c>
-      <c r="J32" t="s">
-        <v>178</v>
-      </c>
       <c r="K32" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L32" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M32" t="s">
         <v>37</v>
@@ -6018,10 +6030,10 @@
         <v>30</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R32" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -6036,7 +6048,7 @@
     </row>
     <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B33" s="7">
         <v>46427</v>
@@ -6058,19 +6070,19 @@
         <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I33" t="s">
+        <v>175</v>
+      </c>
+      <c r="J33" t="s">
+        <v>190</v>
+      </c>
+      <c r="K33" t="s">
         <v>177</v>
       </c>
-      <c r="J33" t="s">
-        <v>192</v>
-      </c>
-      <c r="K33" t="s">
-        <v>179</v>
-      </c>
       <c r="M33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -6079,13 +6091,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q33" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="R33" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -6100,7 +6112,7 @@
     </row>
     <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B34" s="7">
         <v>46427</v>
@@ -6110,31 +6122,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G34" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I34" t="s">
+        <v>175</v>
+      </c>
+      <c r="J34" t="s">
         <v>176</v>
       </c>
-      <c r="I34" t="s">
+      <c r="K34" t="s">
         <v>177</v>
       </c>
-      <c r="J34" t="s">
-        <v>178</v>
-      </c>
-      <c r="K34" t="s">
-        <v>179</v>
-      </c>
       <c r="L34" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M34" t="s">
         <v>75</v>
@@ -6146,13 +6158,13 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Q34" s="8" t="s">
         <v>85</v>
       </c>
       <c r="R34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S34" t="s">
         <v>80</v>
@@ -6167,7 +6179,7 @@
     </row>
     <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B35" s="7">
         <v>46428</v>
@@ -6189,31 +6201,31 @@
         <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J35" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K35" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M35" t="s">
+        <v>263</v>
+      </c>
+      <c r="N35" t="s">
+        <v>30</v>
+      </c>
+      <c r="O35" t="s">
+        <v>29</v>
+      </c>
+      <c r="P35" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q35" s="8" t="s">
         <v>265</v>
-      </c>
-      <c r="N35" t="s">
-        <v>30</v>
-      </c>
-      <c r="O35" t="s">
-        <v>29</v>
-      </c>
-      <c r="P35" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>267</v>
       </c>
       <c r="S35" t="s">
         <v>33</v>
@@ -6228,7 +6240,7 @@
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B36" s="7">
         <v>46428</v>
@@ -6238,10 +6250,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>38</v>
@@ -6250,19 +6262,19 @@
         <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N36" t="s">
         <v>30</v>
@@ -6271,10 +6283,10 @@
         <v>29</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -6289,7 +6301,7 @@
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B37" s="7">
         <v>46430</v>
@@ -6299,7 +6311,7 @@
         <v>Friday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>37</v>
@@ -6311,16 +6323,16 @@
         <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K37" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M37" t="s">
         <v>37</v>
@@ -6332,10 +6344,10 @@
         <v>30</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="R37" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -6350,7 +6362,7 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B38" s="7">
         <v>46441</v>
@@ -6363,7 +6375,7 @@
         <v>36</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>38</v>
@@ -6372,37 +6384,37 @@
         <v>80</v>
       </c>
       <c r="H38" t="s">
+        <v>174</v>
+      </c>
+      <c r="I38" t="s">
+        <v>175</v>
+      </c>
+      <c r="J38" t="s">
         <v>176</v>
       </c>
-      <c r="I38" t="s">
-        <v>177</v>
-      </c>
-      <c r="J38" t="s">
-        <v>178</v>
-      </c>
       <c r="K38" t="s">
+        <v>218</v>
+      </c>
+      <c r="L38" t="s">
+        <v>219</v>
+      </c>
+      <c r="M38" t="s">
+        <v>106</v>
+      </c>
+      <c r="N38" t="s">
+        <v>29</v>
+      </c>
+      <c r="O38" t="s">
+        <v>30</v>
+      </c>
+      <c r="P38" t="s">
         <v>220</v>
       </c>
-      <c r="L38" t="s">
-        <v>221</v>
-      </c>
-      <c r="M38" t="s">
-        <v>108</v>
-      </c>
-      <c r="N38" t="s">
-        <v>29</v>
-      </c>
-      <c r="O38" t="s">
-        <v>30</v>
-      </c>
-      <c r="P38" t="s">
+      <c r="Q38" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="R38" t="s">
         <v>222</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="R38" t="s">
-        <v>224</v>
       </c>
       <c r="S38" t="s">
         <v>33</v>
@@ -6417,7 +6429,7 @@
     </row>
     <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B39" s="7">
         <v>46441</v>
@@ -6427,31 +6439,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G39" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H39" t="s">
+        <v>174</v>
+      </c>
+      <c r="I39" t="s">
+        <v>175</v>
+      </c>
+      <c r="J39" t="s">
         <v>176</v>
       </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>177</v>
       </c>
-      <c r="J39" t="s">
-        <v>178</v>
-      </c>
-      <c r="K39" t="s">
-        <v>179</v>
-      </c>
       <c r="L39" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M39" t="s">
         <v>83</v>
@@ -6463,7 +6475,7 @@
         <v>29</v>
       </c>
       <c r="P39" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Q39" s="8" t="s">
         <v>85</v>
@@ -6484,7 +6496,7 @@
     </row>
     <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B40" s="7">
         <v>46444</v>
@@ -6494,7 +6506,7 @@
         <v>Friday</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>23</v>
@@ -6506,19 +6518,19 @@
         <v>100</v>
       </c>
       <c r="H40" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" t="s">
+        <v>175</v>
+      </c>
+      <c r="J40" t="s">
         <v>176</v>
       </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>177</v>
       </c>
-      <c r="J40" t="s">
+      <c r="L40" t="s">
         <v>178</v>
-      </c>
-      <c r="K40" t="s">
-        <v>179</v>
-      </c>
-      <c r="L40" t="s">
-        <v>180</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -6530,10 +6542,10 @@
         <v>30</v>
       </c>
       <c r="Q40" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="R40" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="S40" t="s">
         <v>33</v>
@@ -6669,7 +6681,7 @@
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B2" s="7">
         <v>46447</v>
@@ -6685,25 +6697,25 @@
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G2" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I2" t="s">
+        <v>319</v>
+      </c>
+      <c r="J2" t="s">
         <v>320</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>321</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>322</v>
-      </c>
-      <c r="K2" t="s">
-        <v>323</v>
-      </c>
-      <c r="L2" t="s">
-        <v>324</v>
       </c>
       <c r="M2" t="s">
         <v>75</v>
@@ -6715,13 +6727,13 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q2" s="8" t="s">
         <v>85</v>
       </c>
       <c r="R2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S2" t="s">
         <v>80</v>
@@ -6736,7 +6748,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B3" s="7">
         <v>46448</v>
@@ -6746,28 +6758,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2">
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M3" t="s">
         <v>52</v>
@@ -6779,10 +6791,10 @@
         <v>30</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="R3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -6797,7 +6809,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B4" s="7">
         <v>46449</v>
@@ -6807,10 +6819,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>38</v>
@@ -6819,34 +6831,34 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J4" t="s">
+        <v>330</v>
+      </c>
+      <c r="K4" t="s">
+        <v>331</v>
+      </c>
+      <c r="M4" t="s">
+        <v>258</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="K4" t="s">
+      <c r="R4" t="s">
         <v>333</v>
-      </c>
-      <c r="M4" t="s">
-        <v>260</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="R4" t="s">
-        <v>335</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -6861,7 +6873,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B5" s="7">
         <v>46450</v>
@@ -6883,19 +6895,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
+        <v>318</v>
+      </c>
+      <c r="I5" t="s">
+        <v>319</v>
+      </c>
+      <c r="J5" t="s">
         <v>320</v>
       </c>
-      <c r="I5" t="s">
-        <v>321</v>
-      </c>
-      <c r="J5" t="s">
-        <v>322</v>
-      </c>
       <c r="K5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M5" t="s">
         <v>37</v>
@@ -6907,13 +6919,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="R5" t="s">
         <v>161</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="R5" t="s">
-        <v>163</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -6928,7 +6940,7 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B6" s="7">
         <v>46455</v>
@@ -6941,7 +6953,7 @@
         <v>79</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>38</v>
@@ -6950,34 +6962,34 @@
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K6" t="s">
+        <v>339</v>
+      </c>
+      <c r="M6" t="s">
+        <v>106</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="R6" t="s">
         <v>341</v>
-      </c>
-      <c r="M6" t="s">
-        <v>108</v>
-      </c>
-      <c r="N6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="R6" t="s">
-        <v>343</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -6992,7 +7004,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B7" s="7">
         <v>46455</v>
@@ -7002,31 +7014,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G7" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H7" t="s">
+        <v>318</v>
+      </c>
+      <c r="I7" t="s">
+        <v>319</v>
+      </c>
+      <c r="J7" t="s">
         <v>320</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>321</v>
       </c>
-      <c r="J7" t="s">
-        <v>322</v>
-      </c>
-      <c r="K7" t="s">
-        <v>323</v>
-      </c>
       <c r="L7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M7" t="s">
         <v>83</v>
@@ -7038,7 +7050,7 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q7" s="8" t="s">
         <v>85</v>
@@ -7059,7 +7071,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B8" s="7">
         <v>46456</v>
@@ -7069,10 +7081,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -7081,19 +7093,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -7102,10 +7114,10 @@
         <v>29</v>
       </c>
       <c r="P8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -7120,7 +7132,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B9" s="7">
         <v>46456</v>
@@ -7142,19 +7154,19 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I9" t="s">
+        <v>319</v>
+      </c>
+      <c r="J9" t="s">
+        <v>330</v>
+      </c>
+      <c r="K9" t="s">
         <v>321</v>
       </c>
-      <c r="J9" t="s">
-        <v>332</v>
-      </c>
-      <c r="K9" t="s">
-        <v>323</v>
-      </c>
       <c r="M9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -7163,13 +7175,13 @@
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="R9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -7184,7 +7196,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B10" s="7">
         <v>46457</v>
@@ -7206,16 +7218,16 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I10" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M10" t="s">
         <v>37</v>
@@ -7227,10 +7239,10 @@
         <v>30</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="R10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -7245,7 +7257,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B11" s="7">
         <v>46462</v>
@@ -7258,7 +7270,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
@@ -7267,22 +7279,22 @@
         <v>80</v>
       </c>
       <c r="H11" t="s">
+        <v>318</v>
+      </c>
+      <c r="I11" t="s">
+        <v>319</v>
+      </c>
+      <c r="J11" t="s">
         <v>320</v>
       </c>
-      <c r="I11" t="s">
-        <v>321</v>
-      </c>
-      <c r="J11" t="s">
-        <v>322</v>
-      </c>
       <c r="K11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L11" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -7291,10 +7303,10 @@
         <v>30</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="R11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -7309,7 +7321,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B12" s="7">
         <v>46462</v>
@@ -7319,7 +7331,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>46</v>
@@ -7331,34 +7343,34 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I12" t="s">
+        <v>319</v>
+      </c>
+      <c r="J12" t="s">
+        <v>330</v>
+      </c>
+      <c r="K12" t="s">
         <v>321</v>
       </c>
-      <c r="J12" t="s">
-        <v>332</v>
-      </c>
-      <c r="K12" t="s">
-        <v>323</v>
-      </c>
       <c r="M12" t="s">
+        <v>356</v>
+      </c>
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="R12" t="s">
         <v>358</v>
-      </c>
-      <c r="N12" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" t="s">
-        <v>30</v>
-      </c>
-      <c r="P12" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="R12" t="s">
-        <v>360</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -7373,7 +7385,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B13" s="7">
         <v>46463</v>
@@ -7395,19 +7407,19 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
+        <v>318</v>
+      </c>
+      <c r="I13" t="s">
+        <v>319</v>
+      </c>
+      <c r="J13" t="s">
         <v>320</v>
       </c>
-      <c r="I13" t="s">
-        <v>321</v>
-      </c>
-      <c r="J13" t="s">
-        <v>322</v>
-      </c>
       <c r="K13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M13" t="s">
         <v>52</v>
@@ -7422,10 +7434,10 @@
         <v>55</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="R13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -7440,7 +7452,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B14" s="7">
         <v>46464</v>
@@ -7450,10 +7462,10 @@
         <v>Thursday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -7462,34 +7474,34 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
+        <v>318</v>
+      </c>
+      <c r="I14" t="s">
+        <v>319</v>
+      </c>
+      <c r="J14" t="s">
         <v>320</v>
       </c>
-      <c r="I14" t="s">
-        <v>321</v>
-      </c>
-      <c r="J14" t="s">
-        <v>322</v>
-      </c>
       <c r="K14" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L14" t="s">
+        <v>365</v>
+      </c>
+      <c r="M14" t="s">
+        <v>258</v>
+      </c>
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="R14" t="s">
         <v>367</v>
-      </c>
-      <c r="M14" t="s">
-        <v>260</v>
-      </c>
-      <c r="N14" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="R14" t="s">
-        <v>369</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -7504,7 +7516,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B15" s="7">
         <v>46468</v>
@@ -7526,19 +7538,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I15" t="s">
+        <v>319</v>
+      </c>
+      <c r="J15" t="s">
         <v>320</v>
       </c>
-      <c r="I15" t="s">
-        <v>321</v>
-      </c>
-      <c r="J15" t="s">
-        <v>322</v>
-      </c>
       <c r="K15" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M15" t="s">
         <v>37</v>
@@ -7550,10 +7562,10 @@
         <v>30</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="R15" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -7568,7 +7580,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B16" s="7">
         <v>46469</v>
@@ -7578,46 +7590,46 @@
         <v>Tuesday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I16" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J16" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K16" t="s">
+        <v>374</v>
+      </c>
+      <c r="M16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N16" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="M16" t="s">
-        <v>120</v>
-      </c>
-      <c r="N16" t="s">
-        <v>29</v>
-      </c>
-      <c r="O16" t="s">
-        <v>30</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="R16" t="s">
         <v>377</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="R16" t="s">
-        <v>379</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -7632,7 +7644,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B17" s="7">
         <v>46470</v>
@@ -7654,19 +7666,19 @@
         <v>80</v>
       </c>
       <c r="H17" t="s">
+        <v>318</v>
+      </c>
+      <c r="I17" t="s">
+        <v>319</v>
+      </c>
+      <c r="J17" t="s">
         <v>320</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>321</v>
       </c>
-      <c r="J17" t="s">
-        <v>322</v>
-      </c>
-      <c r="K17" t="s">
-        <v>323</v>
-      </c>
       <c r="L17" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M17" t="s">
         <v>46</v>
@@ -7678,7 +7690,7 @@
         <v>30</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="R17" t="s">
         <v>49</v>
@@ -7696,7 +7708,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B18" s="7">
         <v>46486</v>
@@ -7706,10 +7718,10 @@
         <v>Friday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>38</v>
@@ -7718,19 +7730,19 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
+        <v>318</v>
+      </c>
+      <c r="I18" t="s">
+        <v>319</v>
+      </c>
+      <c r="J18" t="s">
         <v>320</v>
       </c>
-      <c r="I18" t="s">
-        <v>321</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
+        <v>335</v>
+      </c>
+      <c r="L18" t="s">
         <v>322</v>
-      </c>
-      <c r="K18" t="s">
-        <v>337</v>
-      </c>
-      <c r="L18" t="s">
-        <v>324</v>
       </c>
       <c r="M18" t="s">
         <v>75</v>
@@ -7742,13 +7754,13 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="R18" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -7763,7 +7775,7 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B19" s="7">
         <v>46492</v>
@@ -7785,16 +7797,16 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I19" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K19" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
@@ -7806,13 +7818,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="R19" t="s">
         <v>387</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="R19" t="s">
-        <v>389</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -7827,7 +7839,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B20" s="7">
         <v>46496</v>
@@ -7837,7 +7849,7 @@
         <v>Monday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>23</v>
@@ -7849,19 +7861,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="s">
+        <v>318</v>
+      </c>
+      <c r="I20" t="s">
+        <v>319</v>
+      </c>
+      <c r="J20" t="s">
         <v>320</v>
       </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>321</v>
       </c>
-      <c r="J20" t="s">
-        <v>322</v>
-      </c>
-      <c r="K20" t="s">
-        <v>323</v>
-      </c>
       <c r="L20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -7873,10 +7885,10 @@
         <v>30</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="R20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -7891,7 +7903,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B21" s="7">
         <v>46500</v>
@@ -7901,31 +7913,31 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2">
         <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I21" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -7934,13 +7946,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="R21" t="s">
         <v>395</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="R21" t="s">
-        <v>397</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -7955,7 +7967,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B22" s="7">
         <v>46505</v>
@@ -7965,28 +7977,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2">
         <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I22" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J22" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K22" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M22" t="s">
         <v>52</v>
@@ -7998,10 +8010,10 @@
         <v>30</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="R22" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -8016,7 +8028,7 @@
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B23" s="7">
         <v>46506</v>
@@ -8038,16 +8050,16 @@
         <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I23" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J23" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M23" t="s">
         <v>37</v>
@@ -8059,13 +8071,13 @@
         <v>29</v>
       </c>
       <c r="P23" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="R23" t="s">
         <v>387</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="R23" t="s">
-        <v>389</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -8080,7 +8092,7 @@
     </row>
     <row r="24" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B24" s="7">
         <v>46507</v>
@@ -8090,7 +8102,7 @@
         <v>Friday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
@@ -8102,19 +8114,19 @@
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I24" t="s">
+        <v>319</v>
+      </c>
+      <c r="J24" t="s">
+        <v>330</v>
+      </c>
+      <c r="K24" t="s">
         <v>321</v>
       </c>
-      <c r="J24" t="s">
-        <v>332</v>
-      </c>
-      <c r="K24" t="s">
-        <v>323</v>
-      </c>
       <c r="M24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -8123,13 +8135,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="R24" t="s">
         <v>126</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="R24" t="s">
-        <v>128</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -8144,7 +8156,7 @@
     </row>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B25" s="7">
         <v>46512</v>
@@ -8154,10 +8166,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>38</v>
@@ -8166,34 +8178,34 @@
         <v>80</v>
       </c>
       <c r="H25" t="s">
+        <v>318</v>
+      </c>
+      <c r="I25" t="s">
+        <v>319</v>
+      </c>
+      <c r="J25" t="s">
         <v>320</v>
       </c>
-      <c r="I25" t="s">
-        <v>321</v>
-      </c>
-      <c r="J25" t="s">
-        <v>322</v>
-      </c>
       <c r="K25" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L25" t="s">
+        <v>365</v>
+      </c>
+      <c r="M25" t="s">
+        <v>258</v>
+      </c>
+      <c r="N25" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="R25" t="s">
         <v>367</v>
-      </c>
-      <c r="M25" t="s">
-        <v>260</v>
-      </c>
-      <c r="N25" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="R25" t="s">
-        <v>369</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -8208,7 +8220,7 @@
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B26" s="7">
         <v>46512</v>
@@ -8230,19 +8242,19 @@
         <v>80</v>
       </c>
       <c r="H26" t="s">
+        <v>318</v>
+      </c>
+      <c r="I26" t="s">
+        <v>319</v>
+      </c>
+      <c r="J26" t="s">
         <v>320</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>321</v>
       </c>
-      <c r="J26" t="s">
-        <v>322</v>
-      </c>
-      <c r="K26" t="s">
-        <v>323</v>
-      </c>
       <c r="L26" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M26" t="s">
         <v>46</v>
@@ -8254,7 +8266,7 @@
         <v>30</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="R26" t="s">
         <v>49</v>
@@ -8272,7 +8284,7 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B27" s="7">
         <v>46513</v>
@@ -8282,7 +8294,7 @@
         <v>Thursday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>37</v>
@@ -8294,16 +8306,16 @@
         <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I27" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J27" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K27" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M27" t="s">
         <v>37</v>
@@ -8315,10 +8327,10 @@
         <v>30</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -8333,7 +8345,7 @@
     </row>
     <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B28" s="7">
         <v>46517</v>
@@ -8349,25 +8361,25 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G28" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H28" t="s">
+        <v>318</v>
+      </c>
+      <c r="I28" t="s">
+        <v>319</v>
+      </c>
+      <c r="J28" t="s">
         <v>320</v>
       </c>
-      <c r="I28" t="s">
+      <c r="K28" t="s">
         <v>321</v>
       </c>
-      <c r="J28" t="s">
+      <c r="L28" t="s">
         <v>322</v>
-      </c>
-      <c r="K28" t="s">
-        <v>323</v>
-      </c>
-      <c r="L28" t="s">
-        <v>324</v>
       </c>
       <c r="M28" t="s">
         <v>75</v>
@@ -8379,13 +8391,13 @@
         <v>29</v>
       </c>
       <c r="P28" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q28" s="8" t="s">
         <v>85</v>
       </c>
       <c r="R28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S28" t="s">
         <v>80</v>
@@ -8400,7 +8412,7 @@
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B29" s="7">
         <v>46518</v>
@@ -8413,7 +8425,7 @@
         <v>36</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>38</v>
@@ -8422,22 +8434,22 @@
         <v>80</v>
       </c>
       <c r="H29" t="s">
+        <v>318</v>
+      </c>
+      <c r="I29" t="s">
+        <v>319</v>
+      </c>
+      <c r="J29" t="s">
         <v>320</v>
       </c>
-      <c r="I29" t="s">
-        <v>321</v>
-      </c>
-      <c r="J29" t="s">
-        <v>322</v>
-      </c>
       <c r="K29" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L29" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="M29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N29" t="s">
         <v>29</v>
@@ -8446,13 +8458,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="R29" t="s">
         <v>222</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>413</v>
-      </c>
-      <c r="R29" t="s">
-        <v>224</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -8467,7 +8479,7 @@
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B30" s="7">
         <v>46519</v>
@@ -8477,10 +8489,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -8489,19 +8501,19 @@
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I30" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J30" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K30" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -8510,13 +8522,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="R30" t="s">
         <v>235</v>
-      </c>
-      <c r="Q30" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="R30" t="s">
-        <v>237</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -8531,7 +8543,7 @@
     </row>
     <row r="31" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B31" s="7">
         <v>46520</v>
@@ -8541,7 +8553,7 @@
         <v>Thursday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>83</v>
@@ -8553,16 +8565,16 @@
         <v>80</v>
       </c>
       <c r="H31" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I31" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J31" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K31" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M31" t="s">
         <v>83</v>
@@ -8574,10 +8586,10 @@
         <v>30</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="R31" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -8592,7 +8604,7 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B32" s="7">
         <v>46525</v>
@@ -8614,19 +8626,19 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
+        <v>318</v>
+      </c>
+      <c r="I32" t="s">
+        <v>319</v>
+      </c>
+      <c r="J32" t="s">
         <v>320</v>
       </c>
-      <c r="I32" t="s">
-        <v>321</v>
-      </c>
-      <c r="J32" t="s">
-        <v>322</v>
-      </c>
       <c r="K32" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L32" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M32" t="s">
         <v>52</v>
@@ -8641,10 +8653,10 @@
         <v>55</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="R32" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -8659,7 +8671,7 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B33" s="7">
         <v>46526</v>
@@ -8669,31 +8681,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G33" s="2">
         <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I33" t="s">
+        <v>319</v>
+      </c>
+      <c r="J33" t="s">
+        <v>325</v>
+      </c>
+      <c r="K33" t="s">
         <v>321</v>
       </c>
-      <c r="J33" t="s">
-        <v>327</v>
-      </c>
-      <c r="K33" t="s">
-        <v>323</v>
-      </c>
       <c r="M33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -8702,13 +8714,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="R33" t="s">
         <v>152</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="R33" t="s">
-        <v>154</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -8723,7 +8735,7 @@
     </row>
     <row r="34" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B34" s="7">
         <v>46527</v>
@@ -8745,16 +8757,16 @@
         <v>80</v>
       </c>
       <c r="H34" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I34" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J34" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K34" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s">
         <v>37</v>
@@ -8766,13 +8778,13 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="R34" t="s">
         <v>387</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="R34" t="s">
-        <v>389</v>
       </c>
       <c r="S34" t="s">
         <v>33</v>
@@ -8787,7 +8799,7 @@
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B35" s="7">
         <v>46527</v>
@@ -8797,31 +8809,31 @@
         <v>Thursday</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G35" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H35" t="s">
+        <v>318</v>
+      </c>
+      <c r="I35" t="s">
+        <v>319</v>
+      </c>
+      <c r="J35" t="s">
         <v>320</v>
       </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
         <v>321</v>
       </c>
-      <c r="J35" t="s">
-        <v>322</v>
-      </c>
-      <c r="K35" t="s">
-        <v>323</v>
-      </c>
       <c r="L35" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M35" t="s">
         <v>83</v>
@@ -8833,7 +8845,7 @@
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Q35" s="8" t="s">
         <v>85</v>
@@ -8854,7 +8866,7 @@
     </row>
     <row r="36" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B36" s="7">
         <v>46533</v>
@@ -8864,31 +8876,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G36" s="2">
         <v>12</v>
       </c>
       <c r="H36" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I36" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J36" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K36" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N36" t="s">
         <v>29</v>
@@ -8897,10 +8909,10 @@
         <v>30</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="R36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -8915,7 +8927,7 @@
     </row>
     <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B37" s="7">
         <v>46534</v>
@@ -8925,7 +8937,7 @@
         <v>Thursday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>83</v>
@@ -8937,16 +8949,16 @@
         <v>80</v>
       </c>
       <c r="H37" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I37" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J37" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K37" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s">
         <v>83</v>
@@ -8958,7 +8970,7 @@
         <v>29</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -9088,7 +9100,7 @@
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B2" s="7">
         <v>46546</v>
@@ -9098,31 +9110,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G2" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H2" t="s">
+        <v>431</v>
+      </c>
+      <c r="I2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J2" t="s">
         <v>433</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>434</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>435</v>
-      </c>
-      <c r="K2" t="s">
-        <v>436</v>
-      </c>
-      <c r="L2" t="s">
-        <v>437</v>
       </c>
       <c r="M2" t="s">
         <v>75</v>
@@ -9134,13 +9146,13 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q2" s="8" t="s">
         <v>85</v>
       </c>
       <c r="R2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S2" t="s">
         <v>80</v>
@@ -9155,7 +9167,7 @@
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B3" s="7">
         <v>46547</v>
@@ -9165,7 +9177,7 @@
         <v>Wednesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>83</v>
@@ -9177,19 +9189,19 @@
         <v>80</v>
       </c>
       <c r="H3" t="s">
+        <v>431</v>
+      </c>
+      <c r="I3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J3" t="s">
         <v>433</v>
       </c>
-      <c r="I3" t="s">
-        <v>434</v>
-      </c>
-      <c r="J3" t="s">
-        <v>435</v>
-      </c>
       <c r="K3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="M3" t="s">
         <v>83</v>
@@ -9201,13 +9213,13 @@
         <v>30</v>
       </c>
       <c r="P3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="R3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -9222,7 +9234,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B4" s="7">
         <v>46548</v>
@@ -9244,19 +9256,19 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
+        <v>431</v>
+      </c>
+      <c r="I4" t="s">
+        <v>432</v>
+      </c>
+      <c r="J4" t="s">
         <v>433</v>
       </c>
-      <c r="I4" t="s">
-        <v>434</v>
-      </c>
-      <c r="J4" t="s">
-        <v>435</v>
-      </c>
       <c r="K4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M4" t="s">
         <v>37</v>
@@ -9268,13 +9280,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="R4" t="s">
         <v>161</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="R4" t="s">
-        <v>163</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -9289,7 +9301,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B5" s="7">
         <v>46552</v>
@@ -9299,7 +9311,7 @@
         <v>Monday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
@@ -9311,34 +9323,34 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J5" t="s">
+        <v>447</v>
+      </c>
+      <c r="K5" t="s">
+        <v>438</v>
+      </c>
+      <c r="M5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="R5" t="s">
         <v>449</v>
-      </c>
-      <c r="K5" t="s">
-        <v>440</v>
-      </c>
-      <c r="M5" t="s">
-        <v>96</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="R5" t="s">
-        <v>451</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -9353,7 +9365,7 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B6" s="7">
         <v>46553</v>
@@ -9363,7 +9375,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
@@ -9375,19 +9387,19 @@
         <v>100</v>
       </c>
       <c r="H6" t="s">
+        <v>431</v>
+      </c>
+      <c r="I6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J6" t="s">
         <v>433</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>434</v>
       </c>
-      <c r="J6" t="s">
-        <v>435</v>
-      </c>
-      <c r="K6" t="s">
-        <v>436</v>
-      </c>
       <c r="L6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -9399,10 +9411,10 @@
         <v>30</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="R6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -9417,7 +9429,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B7" s="7">
         <v>46554</v>
@@ -9427,10 +9439,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>38</v>
@@ -9439,19 +9451,19 @@
         <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N7" t="s">
         <v>30</v>
@@ -9460,10 +9472,10 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -9478,7 +9490,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B8" s="7">
         <v>46561</v>
@@ -9500,19 +9512,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J8" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -9521,13 +9533,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="R8" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -9542,7 +9554,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B9" s="7">
         <v>46562</v>
@@ -9555,7 +9567,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>38</v>
@@ -9564,22 +9576,22 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
+        <v>431</v>
+      </c>
+      <c r="I9" t="s">
+        <v>432</v>
+      </c>
+      <c r="J9" t="s">
         <v>433</v>
       </c>
-      <c r="I9" t="s">
-        <v>434</v>
-      </c>
-      <c r="J9" t="s">
-        <v>435</v>
-      </c>
       <c r="K9" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -9588,10 +9600,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="R9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -9606,7 +9618,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B10" s="7">
         <v>46568</v>
@@ -9628,19 +9640,19 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
+        <v>431</v>
+      </c>
+      <c r="I10" t="s">
+        <v>432</v>
+      </c>
+      <c r="J10" t="s">
         <v>433</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>434</v>
       </c>
-      <c r="J10" t="s">
-        <v>435</v>
-      </c>
-      <c r="K10" t="s">
-        <v>436</v>
-      </c>
       <c r="L10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M10" t="s">
         <v>46</v>
@@ -9652,7 +9664,7 @@
         <v>30</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="R10" t="s">
         <v>49</v>
@@ -9670,7 +9682,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B11" s="7">
         <v>46569</v>
@@ -9680,10 +9692,10 @@
         <v>Thursday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
@@ -9692,22 +9704,22 @@
         <v>80</v>
       </c>
       <c r="H11" t="s">
+        <v>431</v>
+      </c>
+      <c r="I11" t="s">
+        <v>432</v>
+      </c>
+      <c r="J11" t="s">
         <v>433</v>
       </c>
-      <c r="I11" t="s">
-        <v>434</v>
-      </c>
-      <c r="J11" t="s">
-        <v>435</v>
-      </c>
       <c r="K11" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -9716,10 +9728,10 @@
         <v>30</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="R11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -9734,7 +9746,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B12" s="7">
         <v>46570</v>
@@ -9750,22 +9762,22 @@
         <v>63</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I12" t="s">
+        <v>432</v>
+      </c>
+      <c r="J12" t="s">
+        <v>467</v>
+      </c>
+      <c r="K12" t="s">
         <v>434</v>
-      </c>
-      <c r="J12" t="s">
-        <v>469</v>
-      </c>
-      <c r="K12" t="s">
-        <v>436</v>
       </c>
       <c r="M12" t="s">
         <v>63</v>
@@ -9777,13 +9789,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="R12" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -9798,7 +9810,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B13" s="7">
         <v>46574</v>
@@ -9814,25 +9826,25 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G13" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H13" t="s">
+        <v>431</v>
+      </c>
+      <c r="I13" t="s">
+        <v>432</v>
+      </c>
+      <c r="J13" t="s">
         <v>433</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>434</v>
       </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
         <v>435</v>
-      </c>
-      <c r="K13" t="s">
-        <v>436</v>
-      </c>
-      <c r="L13" t="s">
-        <v>437</v>
       </c>
       <c r="M13" t="s">
         <v>75</v>
@@ -9844,13 +9856,13 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q13" s="8" t="s">
         <v>85</v>
       </c>
       <c r="R13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S13" t="s">
         <v>80</v>
@@ -9865,7 +9877,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B14" s="7">
         <v>46575</v>
@@ -9887,19 +9899,19 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I14" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K14" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N14" t="s">
         <v>30</v>
@@ -9908,10 +9920,10 @@
         <v>29</v>
       </c>
       <c r="P14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -9926,7 +9938,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B15" s="7">
         <v>46575</v>
@@ -9936,10 +9948,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -9948,19 +9960,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I15" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -9969,10 +9981,10 @@
         <v>29</v>
       </c>
       <c r="P15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -9987,7 +9999,7 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B16" s="7">
         <v>46576</v>
@@ -10009,19 +10021,19 @@
         <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I16" t="s">
+        <v>432</v>
+      </c>
+      <c r="J16" t="s">
+        <v>447</v>
+      </c>
+      <c r="K16" t="s">
         <v>434</v>
       </c>
-      <c r="J16" t="s">
-        <v>449</v>
-      </c>
-      <c r="K16" t="s">
-        <v>436</v>
-      </c>
       <c r="M16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -10030,13 +10042,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="R16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -10051,7 +10063,7 @@
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B17" s="7">
         <v>46582</v>
@@ -10067,25 +10079,25 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H17" t="s">
+        <v>431</v>
+      </c>
+      <c r="I17" t="s">
+        <v>432</v>
+      </c>
+      <c r="J17" t="s">
         <v>433</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>434</v>
       </c>
-      <c r="J17" t="s">
-        <v>435</v>
-      </c>
-      <c r="K17" t="s">
-        <v>436</v>
-      </c>
       <c r="L17" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="M17" t="s">
         <v>83</v>
@@ -10097,7 +10109,7 @@
         <v>29</v>
       </c>
       <c r="P17" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Q17" s="8" t="s">
         <v>85</v>
@@ -10118,7 +10130,7 @@
     </row>
     <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B18" s="7">
         <v>46589</v>
@@ -10140,19 +10152,19 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I18" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J18" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K18" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M18" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
@@ -10161,10 +10173,10 @@
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -10179,7 +10191,7 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B19" s="7">
         <v>46604</v>
@@ -10195,25 +10207,25 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G19" s="15" t="s">
         <v>87</v>
       </c>
       <c r="H19" t="s">
+        <v>431</v>
+      </c>
+      <c r="I19" t="s">
+        <v>432</v>
+      </c>
+      <c r="J19" t="s">
         <v>433</v>
       </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
         <v>434</v>
       </c>
-      <c r="J19" t="s">
+      <c r="L19" t="s">
         <v>435</v>
-      </c>
-      <c r="K19" t="s">
-        <v>436</v>
-      </c>
-      <c r="L19" t="s">
-        <v>437</v>
       </c>
       <c r="M19" t="s">
         <v>75</v>
@@ -10225,13 +10237,13 @@
         <v>29</v>
       </c>
       <c r="P19" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Q19" s="8" t="s">
         <v>85</v>
       </c>
       <c r="R19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S19" t="s">
         <v>80</v>
@@ -10246,7 +10258,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B20" s="7">
         <v>46612</v>
@@ -10256,10 +10268,10 @@
         <v>Friday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>38</v>
@@ -10268,19 +10280,19 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
+        <v>431</v>
+      </c>
+      <c r="I20" t="s">
+        <v>432</v>
+      </c>
+      <c r="J20" t="s">
         <v>433</v>
       </c>
-      <c r="I20" t="s">
-        <v>434</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
+        <v>438</v>
+      </c>
+      <c r="L20" t="s">
         <v>435</v>
-      </c>
-      <c r="K20" t="s">
-        <v>440</v>
-      </c>
-      <c r="L20" t="s">
-        <v>437</v>
       </c>
       <c r="M20" t="s">
         <v>75</v>
@@ -10292,13 +10304,13 @@
         <v>30</v>
       </c>
       <c r="P20" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="R20" t="s">
         <v>486</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="R20" t="s">
-        <v>488</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
